--- a/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_SoilAnalysis.xlsx
+++ b/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_SoilAnalysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2023_F013B4_CO_TILL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6167A1C1-EE22-4B28-ADAD-FAA5289459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5103C3B0-634F-4C30-90B2-39572AEF9731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16365" yWindow="-22260" windowWidth="17970" windowHeight="21285" xr2:uid="{429ECE41-D0F7-47CB-8E0A-4F71261A1319}"/>
+    <workbookView xWindow="-1455" yWindow="-21195" windowWidth="17805" windowHeight="20370" xr2:uid="{429ECE41-D0F7-47CB-8E0A-4F71261A1319}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDF" sheetId="2" r:id="rId1"/>
@@ -1014,6 +1014,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1491,9 +1494,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2003,52 +2009,52 @@
       <c r="D3">
         <v>20</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>8.4</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>7.2</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>0.3</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>1.9</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>6.9</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>7.4</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="4">
         <v>328</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>75.3</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="3">
         <v>1.03</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>7</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="2">
         <v>24.2</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="3">
         <v>3.32</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="4">
         <v>3137</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="4">
         <v>264</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="4">
         <v>541</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="2">
         <v>21.1</v>
       </c>
     </row>
@@ -2065,52 +2071,52 @@
       <c r="D4">
         <v>60</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>8.4</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>7.2</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>1.3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.9</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>5.8</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="4">
         <v>199</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>141.4</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="3">
         <v>0.45</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="2">
         <v>8.6</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="3">
         <v>1.73</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="4">
         <v>4382</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="4">
         <v>234</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="4">
         <v>625</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="2">
         <v>27.1</v>
       </c>
     </row>
@@ -2127,52 +2133,52 @@
       <c r="D5">
         <v>100</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>7.2</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>1.54</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>1.4</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>30</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>5.7</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="4">
         <v>146</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>409.4</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="3">
         <v>0.19</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="2">
         <v>4.3</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="2">
         <v>5.3</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="3">
         <v>0.97</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="4">
         <v>5092</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="4">
         <v>268</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="4">
         <v>910</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="2">
         <v>32</v>
       </c>
     </row>
@@ -2189,52 +2195,52 @@
       <c r="D6">
         <v>140</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>7.2</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <v>0.76</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>12.6</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>6</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="4">
         <v>106</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>134.80000000000001</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="3">
         <v>0.18</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="2">
         <v>3.6</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="2">
         <v>3.5</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="3">
         <v>0.52</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="4">
         <v>5022</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="4">
         <v>248</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="4">
         <v>446</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="2">
         <v>29.4</v>
       </c>
     </row>
@@ -2251,52 +2257,52 @@
       <c r="D7">
         <v>180</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>7.2</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>0.77</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>14.5</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>5.7</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="4">
         <v>110</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>141</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="3">
         <v>0.2</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="2">
         <v>3.7</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="2">
         <v>3.6</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="3">
         <v>0.54</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="4">
         <v>5136</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="4">
         <v>261</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="4">
         <v>513</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="2">
         <v>30.4</v>
       </c>
     </row>
@@ -2313,52 +2319,52 @@
       <c r="D8">
         <v>20</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>8.5</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>7.2</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>1.9</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>4.3</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>6.5</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="4">
         <v>351</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>49.6</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="3">
         <v>1.2</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="2">
         <v>6.8</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="2">
         <v>23.1</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="3">
         <v>3.12</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="4">
         <v>3441</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="4">
         <v>255</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="4">
         <v>469</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="2">
         <v>22.3</v>
       </c>
     </row>
@@ -2375,52 +2381,52 @@
       <c r="D9">
         <v>60</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>8.6</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>7.2</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="3">
         <v>0.45</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>1.3</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>4.5</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>5.7</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="4">
         <v>184</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>94.2</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="3">
         <v>0.51</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="2">
         <v>6</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="2">
         <v>9.1</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="3">
         <v>2.0299999999999998</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="4">
         <v>3916</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="4">
         <v>222</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="4">
         <v>690</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="2">
         <v>24.9</v>
       </c>
     </row>
@@ -2437,52 +2443,52 @@
       <c r="D10">
         <v>100</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>7.2</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="3">
         <v>1.17</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>1.5</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>11</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>5.7</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="4">
         <v>145</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="2">
         <v>182</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="3">
         <v>0.34</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="2">
         <v>4.2</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="2">
         <v>2.8</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="3">
         <v>0.73</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="4">
         <v>5037</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="4">
         <v>259</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="4">
         <v>756</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="2">
         <v>31</v>
       </c>
     </row>
@@ -2499,52 +2505,52 @@
       <c r="D11">
         <v>140</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>8.4</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>7.2</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>1.3</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>3.9</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>5.8</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="4">
         <v>135</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="2">
         <v>255.9</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="3">
         <v>0.3</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="2">
         <v>4.2</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="2">
         <v>1.8</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="3">
         <v>0.45</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="4">
         <v>5295</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="4">
         <v>272</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="4">
         <v>721</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="2">
         <v>32.200000000000003</v>
       </c>
     </row>
@@ -2561,52 +2567,52 @@
       <c r="D12">
         <v>180</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>8.1</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>7.2</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3">
         <v>0.9</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>1</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>5.5</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>5.6</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="4">
         <v>84</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="2">
         <v>153.69999999999999</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="3">
         <v>0.47</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="2">
         <v>3.1</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="2">
         <v>1.7</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="3">
         <v>0.33</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="4">
         <v>5226</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="4">
         <v>246</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="4">
         <v>404</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="2">
         <v>30.1</v>
       </c>
     </row>
@@ -2623,52 +2629,52 @@
       <c r="D13">
         <v>20</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>7.2</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="3">
         <v>1.35</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>1.9</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>3.7</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>7</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="4">
         <v>358</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="2">
         <v>311.3</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="3">
         <v>1.2</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="2">
         <v>6.9</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="2">
         <v>22</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="3">
         <v>3.54</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="4">
         <v>3408</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="4">
         <v>293</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="4">
         <v>1063</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="2">
         <v>25</v>
       </c>
     </row>
@@ -2685,52 +2691,52 @@
       <c r="D14">
         <v>60</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>8.1</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>7.2</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="3">
         <v>1.27</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>1.5</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>5.9</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="4">
         <v>253</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="2">
         <v>299.89999999999998</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="3">
         <v>0.61</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="2">
         <v>7</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="2">
         <v>10.199999999999999</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="3">
         <v>1.98</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="4">
         <v>4549</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="4">
         <v>348</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="4">
         <v>1242</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="2">
         <v>31.7</v>
       </c>
     </row>
@@ -2747,52 +2753,52 @@
       <c r="D15">
         <v>100</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>7.2</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="3">
         <v>1.46</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>1.3</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>3</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>5.8</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="4">
         <v>119</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="2">
         <v>209.8</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="3">
         <v>0.48</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="2">
         <v>4</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="2">
         <v>4.3</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="3">
         <v>0.73</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="4">
         <v>5221</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="4">
         <v>292</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="4">
         <v>787</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="2">
         <v>32.299999999999997</v>
       </c>
     </row>
@@ -2809,52 +2815,52 @@
       <c r="D16">
         <v>140</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>7.2</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="3">
         <v>1.05</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>2.5</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>5.5</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="4">
         <v>70</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="2">
         <v>157.5</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="3">
         <v>0.36</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="2">
         <v>3.3</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="3">
         <v>0.43</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="4">
         <v>4846</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="4">
         <v>235</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="4">
         <v>387</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="2">
         <v>28</v>
       </c>
     </row>
@@ -2871,52 +2877,52 @@
       <c r="D17">
         <v>180</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>7.2</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="3">
         <v>0.93</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>1.2</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>1.9</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="2">
         <v>5.9</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="4">
         <v>80</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="2">
         <v>95.2</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="3">
         <v>0.4</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="2">
         <v>3.5</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="2">
         <v>1.4</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="4">
         <v>5120</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="4">
         <v>267</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="4">
         <v>353</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="2">
         <v>29.6</v>
       </c>
     </row>
@@ -2933,52 +2939,52 @@
       <c r="D18">
         <v>20</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>8.4</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>7.2</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="3">
         <v>0.41</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>1.8</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>1.3</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="2">
         <v>7</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="4">
         <v>311</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="2">
         <v>42.4</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="3">
         <v>0.99</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="2">
         <v>6.9</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="2">
         <v>22.7</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="3">
         <v>3.47</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="4">
         <v>3360</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="4">
         <v>267</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="4">
         <v>536</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="2">
         <v>22.2</v>
       </c>
     </row>
@@ -2995,52 +3001,52 @@
       <c r="D19">
         <v>60</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>8.6</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>7.2</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="3">
         <v>0.7</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>1.2</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>2.7</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="2">
         <v>5.9</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="4">
         <v>198</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="2">
         <v>117.9</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="3">
         <v>0.25</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="2">
         <v>5.3</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="2">
         <v>7.9</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="3">
         <v>1.68</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="4">
         <v>3833</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="4">
         <v>232</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="4">
         <v>677</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="2">
         <v>24.5</v>
       </c>
     </row>
@@ -3057,52 +3063,52 @@
       <c r="D20">
         <v>100</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>7.2</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="3">
         <v>1.33</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>1.3</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>6.1</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="2">
         <v>5.7</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="4">
         <v>117</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="2">
         <v>205.9</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="3">
         <v>0.16</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="2">
         <v>3</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="3">
         <v>0.76</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="4">
         <v>4605</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="4">
         <v>235</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="4">
         <v>746</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="2">
         <v>28.5</v>
       </c>
     </row>
@@ -3119,52 +3125,52 @@
       <c r="D21">
         <v>140</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>7.2</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="3">
         <v>1.39</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>1.2</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>6.2</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="2">
         <v>6.2</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="4">
         <v>89</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="2">
         <v>265.2</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="2">
         <v>3.7</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="2">
         <v>2.5</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="3">
         <v>0.5</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="4">
         <v>4610</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="4">
         <v>241</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="4">
         <v>487</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="2">
         <v>27.4</v>
       </c>
     </row>
@@ -3181,52 +3187,52 @@
       <c r="D22">
         <v>180</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>8.4</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>7.2</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="3">
         <v>0.84</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>1</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>3.4</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="2">
         <v>5</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="4">
         <v>74</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="2">
         <v>103.9</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="3">
         <v>0.19</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="2">
         <v>3.9</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="3">
         <v>0.36</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="4">
         <v>4426</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="4">
         <v>202</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="4">
         <v>324</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="2">
         <v>25.4</v>
       </c>
     </row>
@@ -3243,52 +3249,52 @@
       <c r="D23">
         <v>20</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>8.5</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>7.2</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="3">
         <v>0.52</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>2</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>3.1</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="2">
         <v>6.3</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="4">
         <v>268</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="2">
         <v>56.2</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="3">
         <v>1.2</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="2">
         <v>6.3</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="2">
         <v>17.8</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="3">
         <v>3.48</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="4">
         <v>2350</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="4">
         <v>207</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="4">
         <v>400</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="2">
         <v>15.9</v>
       </c>
     </row>
@@ -3305,52 +3311,52 @@
       <c r="D24">
         <v>60</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <v>8.4</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>7.2</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="3">
         <v>1.01</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="2">
         <v>1.4</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>8.1</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="2">
         <v>5.9</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="4">
         <v>164</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="2">
         <v>121.4</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="3">
         <v>0.65</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="2">
         <v>4.3</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="2">
         <v>6.3</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="3">
         <v>1.72</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="4">
         <v>3628</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="4">
         <v>261</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="4">
         <v>576</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="2">
         <v>23.2</v>
       </c>
     </row>
@@ -3367,52 +3373,52 @@
       <c r="D25">
         <v>100</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="2">
         <v>8.4</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <v>7.2</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="3">
         <v>0.96</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>1</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>7.9</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="2">
         <v>6</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="4">
         <v>136</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="2">
         <v>171.5</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="3">
         <v>0.74</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="2">
         <v>4.8</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="3">
         <v>0.74</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="4">
         <v>3734</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="4">
         <v>218</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="4">
         <v>786</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="2">
         <v>24.3</v>
       </c>
     </row>
@@ -3429,52 +3435,52 @@
       <c r="D26">
         <v>140</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>7.2</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="3">
         <v>1.04</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="2">
         <v>1.2</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="2">
         <v>5.5</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="4">
         <v>116</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="2">
         <v>259.10000000000002</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="3">
         <v>0.46</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="2">
         <v>3.7</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="3">
         <v>0.75</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="4">
         <v>4158</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="4">
         <v>226</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="4">
         <v>551</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="2">
         <v>25.4</v>
       </c>
     </row>
@@ -3491,52 +3497,52 @@
       <c r="D27">
         <v>180</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>7.2</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="3">
         <v>0.94</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>2.5</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="2">
         <v>6.2</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="4">
         <v>89</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="2">
         <v>91.1</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="3">
         <v>0.69</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="2">
         <v>4.3</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="3">
         <v>0.54</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="4">
         <v>4563</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="4">
         <v>236</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="4">
         <v>384</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="2">
         <v>26.7</v>
       </c>
     </row>
@@ -3553,52 +3559,52 @@
       <c r="D28">
         <v>20</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>7.2</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="3">
         <v>0.9</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="2">
         <v>1.8</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>3.7</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="2">
         <v>7.2</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="4">
         <v>325</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="2">
         <v>148</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="3">
         <v>1.03</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="2">
         <v>6.9</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="2">
         <v>24.1</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="3">
         <v>3.27</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="4">
         <v>3173</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="4">
         <v>235</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="4">
         <v>542</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="2">
         <v>21</v>
       </c>
     </row>
@@ -3615,52 +3621,52 @@
       <c r="D29">
         <v>60</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2">
         <v>8.4</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <v>7.2</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="3">
         <v>1.25</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="2">
         <v>1.5</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>10.9</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="2">
         <v>6.2</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="4">
         <v>197</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="2">
         <v>146.4</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="2">
         <v>9.5</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="3">
         <v>1.58</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="4">
         <v>4574</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="4">
         <v>264</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="4">
         <v>913</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="2">
         <v>29.5</v>
       </c>
     </row>
@@ -3677,52 +3683,52 @@
       <c r="D30">
         <v>100</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="2">
         <v>7.2</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="3">
         <v>1.38</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="2">
         <v>1.5</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="2">
         <v>4.3</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="2">
         <v>6</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="4">
         <v>128</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="2">
         <v>228.1</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="3">
         <v>0.25</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="2">
         <v>4.3</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="3">
         <v>0.8</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="4">
         <v>4907</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="4">
         <v>277</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="4">
         <v>755</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="2">
         <v>30.5</v>
       </c>
     </row>
@@ -3739,52 +3745,52 @@
       <c r="D31">
         <v>140</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="2">
         <v>7.2</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <v>1.2</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="2">
         <v>1.2</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="2">
         <v>1.9</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="2">
         <v>5.6</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="4">
         <v>89</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="2">
         <v>110.5</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="3">
         <v>0.12</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="2">
         <v>3.4</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="2">
         <v>1.7</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="3">
         <v>0.43</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="4">
         <v>4716</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="4">
         <v>267</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="4">
         <v>436</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="2">
         <v>27.9</v>
       </c>
     </row>
@@ -3801,52 +3807,52 @@
       <c r="D32">
         <v>180</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="2">
         <v>8.5</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="2">
         <v>7.2</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="3">
         <v>0.54</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="2">
         <v>1</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="2">
         <v>6.1</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="4">
         <v>101</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="2">
         <v>60.8</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="3">
         <v>0.24</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="2">
         <v>3.4</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="2">
         <v>3.9</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="3">
         <v>0.67</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="4">
         <v>4224</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="4">
         <v>231</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="4">
         <v>282</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="2">
         <v>24.5</v>
       </c>
     </row>
@@ -3863,52 +3869,52 @@
       <c r="D33">
         <v>20</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="2">
         <v>8.5</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="2">
         <v>7.2</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="3">
         <v>0.84</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="2">
         <v>1.8</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="2">
         <v>3.6</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="2">
         <v>5.9</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="4">
         <v>258</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="2">
         <v>89.4</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="3">
         <v>0.6</v>
       </c>
-      <c r="N33">
+      <c r="N33" s="2">
         <v>3.6</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="2">
         <v>5.9</v>
       </c>
-      <c r="P33">
+      <c r="P33" s="3">
         <v>2</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="4">
         <v>4025</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="4">
         <v>285</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="4">
         <v>652</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="2">
         <v>26</v>
       </c>
     </row>
@@ -3925,52 +3931,52 @@
       <c r="D34">
         <v>60</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="2">
         <v>8.5</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2">
         <v>7.2</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <v>0.84</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="2">
         <v>1.4</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="2">
         <v>2</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="2">
         <v>5.9</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="4">
         <v>150</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="2">
         <v>87.3</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="2">
         <v>3.8</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="2">
         <v>6.2</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="3">
         <v>1.25</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="4">
         <v>4746</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="4">
         <v>240</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="4">
         <v>717</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="2">
         <v>29.2</v>
       </c>
     </row>
@@ -3987,52 +3993,52 @@
       <c r="D35">
         <v>100</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="2">
         <v>8.4</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="2">
         <v>7.2</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <v>0.9</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="2">
         <v>1.5</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="2">
         <v>3.3</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="2">
         <v>5.6</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="4">
         <v>109</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="2">
         <v>178.6</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="3">
         <v>0.11</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="2">
         <v>1.8</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="3">
         <v>0.53</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="4">
         <v>4860</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="4">
         <v>284</v>
       </c>
-      <c r="S35">
+      <c r="S35" s="4">
         <v>674</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="2">
         <v>29.9</v>
       </c>
     </row>
@@ -4049,52 +4055,52 @@
       <c r="D36">
         <v>140</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="2">
         <v>7.2</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="3">
         <v>0.69</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="2">
         <v>1.2</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="2">
         <v>3.7</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="2">
         <v>5.9</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="4">
         <v>95</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="2">
         <v>131.9</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="3">
         <v>0.16</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="2">
         <v>3.6</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="2">
         <v>1.4</v>
       </c>
-      <c r="P36">
+      <c r="P36" s="3">
         <v>0.37</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" s="4">
         <v>4784</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="4">
         <v>278</v>
       </c>
-      <c r="S36">
+      <c r="S36" s="4">
         <v>491</v>
       </c>
-      <c r="T36">
+      <c r="T36" s="2">
         <v>28.6</v>
       </c>
     </row>
@@ -4111,52 +4117,52 @@
       <c r="D37">
         <v>180</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="2">
         <v>7.2</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="3">
         <v>0.63</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="2">
         <v>1</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="2">
         <v>3.7</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="2">
         <v>5.8</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="4">
         <v>72</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="2">
         <v>83.7</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="3">
         <v>0.34</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="2">
         <v>3.9</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="2">
         <v>1.5</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="3">
         <v>0.39</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="4">
         <v>4307</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="4">
         <v>213</v>
       </c>
-      <c r="S37">
+      <c r="S37" s="4">
         <v>288</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="2">
         <v>24.7</v>
       </c>
     </row>
@@ -4173,52 +4179,52 @@
       <c r="D38">
         <v>20</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="2">
         <v>7.2</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="3">
         <v>0.3</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="2">
         <v>1.7</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="2">
         <v>3.9</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="2">
         <v>6.9</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="4">
         <v>263</v>
       </c>
-      <c r="L38">
+      <c r="L38" s="2">
         <v>25</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="3">
         <v>1.05</v>
       </c>
-      <c r="N38">
+      <c r="N38" s="2">
         <v>5.4</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="2">
         <v>14.1</v>
       </c>
-      <c r="P38">
+      <c r="P38" s="3">
         <v>2.93</v>
       </c>
-      <c r="Q38">
+      <c r="Q38" s="4">
         <v>2101</v>
       </c>
-      <c r="R38">
+      <c r="R38" s="4">
         <v>203</v>
       </c>
-      <c r="S38">
+      <c r="S38" s="4">
         <v>295</v>
       </c>
-      <c r="T38">
+      <c r="T38" s="2">
         <v>14.2</v>
       </c>
     </row>
@@ -4235,52 +4241,52 @@
       <c r="D39">
         <v>60</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2">
         <v>7.2</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="3">
         <v>0.32</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="2">
         <v>1.2</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="2">
         <v>0.9</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="2">
         <v>6</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="4">
         <v>192</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="2">
         <v>46.6</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="3">
         <v>0.31</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="2">
         <v>5.2</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="2">
         <v>8.4</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="3">
         <v>1.59</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="4">
         <v>2366</v>
       </c>
-      <c r="R39">
+      <c r="R39" s="4">
         <v>227</v>
       </c>
-      <c r="S39">
+      <c r="S39" s="4">
         <v>518</v>
       </c>
-      <c r="T39">
+      <c r="T39" s="2">
         <v>16.5</v>
       </c>
     </row>
@@ -4297,52 +4303,52 @@
       <c r="D40">
         <v>100</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="2">
         <v>8.5</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="2">
         <v>7.2</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="3">
         <v>0.47</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="2">
         <v>1</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="2">
         <v>2.7</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="2">
         <v>5.7</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="4">
         <v>130</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="2">
         <v>66.599999999999994</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="3">
         <v>0.19</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="2">
         <v>4.5</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="3">
         <v>0.85</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="4">
         <v>3427</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="4">
         <v>188</v>
       </c>
-      <c r="S40">
+      <c r="S40" s="4">
         <v>464</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="2">
         <v>21.1</v>
       </c>
     </row>
@@ -4359,52 +4365,52 @@
       <c r="D41">
         <v>140</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="2">
         <v>7.2</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="3">
         <v>0.68</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="2">
         <v>1</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="2">
         <v>3.2</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="2">
         <v>6.2</v>
       </c>
-      <c r="K41">
+      <c r="K41" s="4">
         <v>138</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="2">
         <v>113.7</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="3">
         <v>0.27</v>
       </c>
-      <c r="N41">
+      <c r="N41" s="2">
         <v>4</v>
       </c>
-      <c r="O41">
+      <c r="O41" s="2">
         <v>2.9</v>
       </c>
-      <c r="P41">
+      <c r="P41" s="3">
         <v>0.52</v>
       </c>
-      <c r="Q41">
+      <c r="Q41" s="4">
         <v>4426</v>
       </c>
-      <c r="R41">
+      <c r="R41" s="4">
         <v>204</v>
       </c>
-      <c r="S41">
+      <c r="S41" s="4">
         <v>694</v>
       </c>
-      <c r="T41">
+      <c r="T41" s="2">
         <v>27.2</v>
       </c>
     </row>
@@ -4421,52 +4427,52 @@
       <c r="D42">
         <v>180</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="2">
         <v>8.1</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="2">
         <v>7.2</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <v>0.71</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="2">
         <v>1.2</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="2">
         <v>6.1</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="2">
         <v>5.6</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="4">
         <v>116</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="2">
         <v>187.8</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="3">
         <v>0.24</v>
       </c>
-      <c r="N42">
+      <c r="N42" s="2">
         <v>4.3</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="2">
         <v>3.2</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="3">
         <v>0.5</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="4">
         <v>4697</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="4">
         <v>214</v>
       </c>
-      <c r="S42">
+      <c r="S42" s="4">
         <v>525</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="2">
         <v>27.9</v>
       </c>
     </row>
@@ -4483,52 +4489,52 @@
       <c r="D43">
         <v>20</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="2">
         <v>7.2</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="3">
         <v>0.34</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="2">
         <v>1.9</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="2">
         <v>2.6</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="2">
         <v>6.7</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="4">
         <v>342</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="2">
         <v>42</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="3">
         <v>1.05</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="2">
         <v>5.7</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="2">
         <v>18</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="3">
         <v>3.09</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="4">
         <v>2666</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="4">
         <v>257</v>
       </c>
-      <c r="S43">
+      <c r="S43" s="4">
         <v>448</v>
       </c>
-      <c r="T43">
+      <c r="T43" s="2">
         <v>18.3</v>
       </c>
     </row>
@@ -4545,52 +4551,52 @@
       <c r="D44">
         <v>60</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="2">
         <v>7.2</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <v>0.54</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="2">
         <v>1.5</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="2">
         <v>5.6</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="4">
         <v>180</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="2">
         <v>101.2</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="3">
         <v>0.32</v>
       </c>
-      <c r="N44">
+      <c r="N44" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O44">
+      <c r="O44" s="2">
         <v>6.8</v>
       </c>
-      <c r="P44">
+      <c r="P44" s="3">
         <v>1.6</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="4">
         <v>3580</v>
       </c>
-      <c r="R44">
+      <c r="R44" s="4">
         <v>301</v>
       </c>
-      <c r="S44">
+      <c r="S44" s="4">
         <v>607</v>
       </c>
-      <c r="T44">
+      <c r="T44" s="2">
         <v>23.5</v>
       </c>
     </row>
@@ -4607,52 +4613,52 @@
       <c r="D45">
         <v>100</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="2">
         <v>8.4</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="2">
         <v>7.2</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <v>0.84</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="2">
         <v>1.6</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="2">
         <v>5.2</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="2">
         <v>5.9</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="4">
         <v>155</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="2">
         <v>128.80000000000001</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="3">
         <v>0.26</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="2">
         <v>5.3</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="3">
         <v>0.86</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="4">
         <v>4894</v>
       </c>
-      <c r="R45">
+      <c r="R45" s="4">
         <v>301</v>
       </c>
-      <c r="S45">
+      <c r="S45" s="4">
         <v>1023</v>
       </c>
-      <c r="T45">
+      <c r="T45" s="2">
         <v>31.8</v>
       </c>
     </row>
@@ -4669,52 +4675,52 @@
       <c r="D46">
         <v>140</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="2">
         <v>7.2</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="3">
         <v>0.66</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="2">
         <v>1.3</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="2">
         <v>5.8</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="4">
         <v>115</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="2">
         <v>136.19999999999999</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="3">
         <v>0.2</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="2">
         <v>3.7</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="2">
         <v>3.9</v>
       </c>
-      <c r="P46">
+      <c r="P46" s="3">
         <v>0.64</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="4">
         <v>4805</v>
       </c>
-      <c r="R46">
+      <c r="R46" s="4">
         <v>302</v>
       </c>
-      <c r="S46">
+      <c r="S46" s="4">
         <v>565</v>
       </c>
-      <c r="T46">
+      <c r="T46" s="2">
         <v>29.3</v>
       </c>
     </row>
@@ -4731,52 +4737,52 @@
       <c r="D47">
         <v>180</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="2">
         <v>8.1</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="2">
         <v>7.2</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="3">
         <v>0.52</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="2">
         <v>1.5</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="2">
         <v>6</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="4">
         <v>149</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="2">
         <v>112.3</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="3">
         <v>0.59</v>
       </c>
-      <c r="N47">
+      <c r="N47" s="2">
         <v>3.8</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="2">
         <v>6.6</v>
       </c>
-      <c r="P47">
+      <c r="P47" s="3">
         <v>0.97</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="4">
         <v>4870</v>
       </c>
-      <c r="R47">
+      <c r="R47" s="4">
         <v>320</v>
       </c>
-      <c r="S47">
+      <c r="S47" s="4">
         <v>453</v>
       </c>
-      <c r="T47">
+      <c r="T47" s="2">
         <v>29.4</v>
       </c>
     </row>
@@ -4793,52 +4799,52 @@
       <c r="D48">
         <v>20</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="2">
         <v>8.4</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="2">
         <v>7.2</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="3">
         <v>0.76</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="2">
         <v>1.7</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="2">
         <v>2.5</v>
       </c>
-      <c r="J48">
+      <c r="J48" s="2">
         <v>6.9</v>
       </c>
-      <c r="K48">
+      <c r="K48" s="4">
         <v>277</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="2">
         <v>61.2</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="3">
         <v>0.96</v>
       </c>
-      <c r="N48">
+      <c r="N48" s="2">
         <v>6.9</v>
       </c>
-      <c r="O48">
+      <c r="O48" s="2">
         <v>19.3</v>
       </c>
-      <c r="P48">
+      <c r="P48" s="3">
         <v>3.17</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="4">
         <v>2960</v>
       </c>
-      <c r="R48">
+      <c r="R48" s="4">
         <v>248</v>
       </c>
-      <c r="S48">
+      <c r="S48" s="4">
         <v>618</v>
       </c>
-      <c r="T48">
+      <c r="T48" s="2">
         <v>20.3</v>
       </c>
     </row>
@@ -4855,52 +4861,52 @@
       <c r="D49">
         <v>60</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="2">
         <v>8.5</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="2">
         <v>7.2</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="3">
         <v>2.04</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="2">
         <v>1.3</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="J49">
+      <c r="J49" s="2">
         <v>6</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="4">
         <v>175</v>
       </c>
-      <c r="L49">
+      <c r="L49" s="2">
         <v>164.7</v>
       </c>
-      <c r="M49">
+      <c r="M49" s="3">
         <v>0.32</v>
       </c>
-      <c r="N49">
+      <c r="N49" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O49">
+      <c r="O49" s="2">
         <v>7.4</v>
       </c>
-      <c r="P49">
+      <c r="P49" s="3">
         <v>1.39</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="4">
         <v>4565</v>
       </c>
-      <c r="R49">
+      <c r="R49" s="4">
         <v>296</v>
       </c>
-      <c r="S49">
+      <c r="S49" s="4">
         <v>1003</v>
       </c>
-      <c r="T49">
+      <c r="T49" s="2">
         <v>30.1</v>
       </c>
     </row>
@@ -4917,52 +4923,52 @@
       <c r="D50">
         <v>100</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="2">
         <v>7.2</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="3">
         <v>1.94</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="2">
         <v>1.2</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="2">
         <v>2.8</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="2">
         <v>6.1</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="4">
         <v>111</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="2">
         <v>185.7</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="3">
         <v>0.3</v>
       </c>
-      <c r="N50">
+      <c r="N50" s="2">
         <v>4</v>
       </c>
-      <c r="O50">
+      <c r="O50" s="2">
         <v>2.7</v>
       </c>
-      <c r="P50">
+      <c r="P50" s="3">
         <v>0.65</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="4">
         <v>4712</v>
       </c>
-      <c r="R50">
+      <c r="R50" s="4">
         <v>275</v>
       </c>
-      <c r="S50">
+      <c r="S50" s="4">
         <v>731</v>
       </c>
-      <c r="T50">
+      <c r="T50" s="2">
         <v>29.3</v>
       </c>
     </row>
@@ -4979,52 +4985,52 @@
       <c r="D51">
         <v>140</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="2">
         <v>7.2</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="3">
         <v>1.3</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="2">
         <v>1.2</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="2">
         <v>1.9</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="2">
         <v>5.7</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="4">
         <v>92</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="2">
         <v>98.9</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="3">
         <v>0.18</v>
       </c>
-      <c r="N51">
+      <c r="N51" s="2">
         <v>3.4</v>
       </c>
-      <c r="O51">
+      <c r="O51" s="2">
         <v>1.6</v>
       </c>
-      <c r="P51">
+      <c r="P51" s="3">
         <v>0.43</v>
       </c>
-      <c r="Q51">
+      <c r="Q51" s="4">
         <v>4517</v>
       </c>
-      <c r="R51">
+      <c r="R51" s="4">
         <v>278</v>
       </c>
-      <c r="S51">
+      <c r="S51" s="4">
         <v>398</v>
       </c>
-      <c r="T51">
+      <c r="T51" s="2">
         <v>26.9</v>
       </c>
     </row>
@@ -5041,52 +5047,52 @@
       <c r="D52">
         <v>180</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="2">
         <v>8.1</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="2">
         <v>7.2</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="3">
         <v>1.05</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="2">
         <v>1.7</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="4">
         <v>81</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="2">
         <v>72.3</v>
       </c>
-      <c r="M52">
+      <c r="M52" s="3">
         <v>0.16</v>
       </c>
-      <c r="N52">
+      <c r="N52" s="2">
         <v>2.4</v>
       </c>
-      <c r="O52">
+      <c r="O52" s="2">
         <v>1.2</v>
       </c>
-      <c r="P52">
+      <c r="P52" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q52">
+      <c r="Q52" s="4">
         <v>4217</v>
       </c>
-      <c r="R52">
+      <c r="R52" s="4">
         <v>268</v>
       </c>
-      <c r="S52">
+      <c r="S52" s="4">
         <v>262</v>
       </c>
-      <c r="T52">
+      <c r="T52" s="2">
         <v>24.7</v>
       </c>
     </row>
@@ -5103,52 +5109,52 @@
       <c r="D53">
         <v>20</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="2">
         <v>8.4</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="2">
         <v>7.2</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="3">
         <v>0.95</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="2">
         <v>1.9</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="2">
         <v>3.1</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="2">
         <v>7.2</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="4">
         <v>286</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="2">
         <v>97.2</v>
       </c>
-      <c r="M53">
+      <c r="M53" s="3">
         <v>0.98</v>
       </c>
-      <c r="N53">
+      <c r="N53" s="2">
         <v>6.2</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="2">
         <v>21.4</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="3">
         <v>3.14</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="4">
         <v>2471</v>
       </c>
-      <c r="R53">
+      <c r="R53" s="4">
         <v>234</v>
       </c>
-      <c r="S53">
+      <c r="S53" s="4">
         <v>524</v>
       </c>
-      <c r="T53">
+      <c r="T53" s="2">
         <v>17.3</v>
       </c>
     </row>
@@ -5165,52 +5171,52 @@
       <c r="D54">
         <v>60</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="2">
         <v>7.2</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <v>1.58</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="2">
         <v>1.2</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="2">
         <v>4.8</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="2">
         <v>6.2</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="4">
         <v>153</v>
       </c>
-      <c r="L54">
+      <c r="L54" s="2">
         <v>158.30000000000001</v>
       </c>
-      <c r="M54">
+      <c r="M54" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N54">
+      <c r="N54" s="2">
         <v>4.8</v>
       </c>
-      <c r="O54">
+      <c r="O54" s="2">
         <v>6.8</v>
       </c>
-      <c r="P54">
+      <c r="P54" s="3">
         <v>1.36</v>
       </c>
-      <c r="Q54">
+      <c r="Q54" s="4">
         <v>3736</v>
       </c>
-      <c r="R54">
+      <c r="R54" s="4">
         <v>213</v>
       </c>
-      <c r="S54">
+      <c r="S54" s="4">
         <v>644</v>
       </c>
-      <c r="T54">
+      <c r="T54" s="2">
         <v>23.6</v>
       </c>
     </row>
@@ -5227,52 +5233,52 @@
       <c r="D55">
         <v>100</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="2">
         <v>8.1</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="2">
         <v>7.2</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <v>3.76</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="2">
         <v>1.3</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="2">
         <v>7.9</v>
       </c>
-      <c r="J55">
+      <c r="J55" s="2">
         <v>5.8</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="4">
         <v>127</v>
       </c>
-      <c r="L55">
+      <c r="L55" s="2">
         <v>301.89999999999998</v>
       </c>
-      <c r="M55">
+      <c r="M55" s="3">
         <v>0.24</v>
       </c>
-      <c r="N55">
+      <c r="N55" s="2">
         <v>4.3</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="2">
         <v>2.9</v>
       </c>
-      <c r="P55">
+      <c r="P55" s="3">
         <v>0.67</v>
       </c>
-      <c r="Q55">
+      <c r="Q55" s="4">
         <v>4897</v>
       </c>
-      <c r="R55">
+      <c r="R55" s="4">
         <v>263</v>
       </c>
-      <c r="S55">
+      <c r="S55" s="4">
         <v>736</v>
       </c>
-      <c r="T55">
+      <c r="T55" s="2">
         <v>30.2</v>
       </c>
     </row>
@@ -5289,52 +5295,52 @@
       <c r="D56">
         <v>140</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="2">
         <v>7.2</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <v>1.58</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="2">
         <v>1.3</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J56">
+      <c r="J56" s="2">
         <v>5.7</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="4">
         <v>87</v>
       </c>
-      <c r="L56">
+      <c r="L56" s="2">
         <v>103.9</v>
       </c>
-      <c r="M56">
+      <c r="M56" s="3">
         <v>0.27</v>
       </c>
-      <c r="N56">
+      <c r="N56" s="2">
         <v>2.9</v>
       </c>
-      <c r="O56">
+      <c r="O56" s="2">
         <v>1.9</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="3">
         <v>0.41</v>
       </c>
-      <c r="Q56">
+      <c r="Q56" s="4">
         <v>4709</v>
       </c>
-      <c r="R56">
+      <c r="R56" s="4">
         <v>223</v>
       </c>
-      <c r="S56">
+      <c r="S56" s="4">
         <v>358</v>
       </c>
-      <c r="T56">
+      <c r="T56" s="2">
         <v>27.2</v>
       </c>
     </row>
@@ -5351,52 +5357,52 @@
       <c r="D57">
         <v>180</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="2">
         <v>8.1</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="2">
         <v>7.2</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <v>1.1599999999999999</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="2">
         <v>1.9</v>
       </c>
-      <c r="J57">
+      <c r="J57" s="2">
         <v>5.8</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="4">
         <v>92</v>
       </c>
-      <c r="L57">
+      <c r="L57" s="2">
         <v>50.8</v>
       </c>
-      <c r="M57">
+      <c r="M57" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N57">
+      <c r="N57" s="2">
         <v>3.2</v>
       </c>
-      <c r="O57">
+      <c r="O57" s="2">
         <v>2.1</v>
       </c>
-      <c r="P57">
+      <c r="P57" s="3">
         <v>0.38</v>
       </c>
-      <c r="Q57">
+      <c r="Q57" s="4">
         <v>4429</v>
       </c>
-      <c r="R57">
+      <c r="R57" s="4">
         <v>232</v>
       </c>
-      <c r="S57">
+      <c r="S57" s="4">
         <v>246</v>
       </c>
-      <c r="T57">
+      <c r="T57" s="2">
         <v>25.4</v>
       </c>
     </row>
@@ -5413,52 +5419,52 @@
       <c r="D58">
         <v>20</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="2">
         <v>8.4</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="2">
         <v>7.2</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="3">
         <v>0.3</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="2">
         <v>1.8</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="2">
         <v>1.6</v>
       </c>
-      <c r="J58">
+      <c r="J58" s="2">
         <v>6.4</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="4">
         <v>241</v>
       </c>
-      <c r="L58">
+      <c r="L58" s="2">
         <v>25.4</v>
       </c>
-      <c r="M58">
+      <c r="M58" s="3">
         <v>0.84</v>
       </c>
-      <c r="N58">
+      <c r="N58" s="2">
         <v>7.4</v>
       </c>
-      <c r="O58">
+      <c r="O58" s="2">
         <v>17.8</v>
       </c>
-      <c r="P58">
+      <c r="P58" s="3">
         <v>3.04</v>
       </c>
-      <c r="Q58">
+      <c r="Q58" s="4">
         <v>2861</v>
       </c>
-      <c r="R58">
+      <c r="R58" s="4">
         <v>257</v>
       </c>
-      <c r="S58">
+      <c r="S58" s="4">
         <v>504</v>
       </c>
-      <c r="T58">
+      <c r="T58" s="2">
         <v>19.3</v>
       </c>
     </row>
@@ -5475,52 +5481,52 @@
       <c r="D59">
         <v>60</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="2">
         <v>8.6</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="2">
         <v>7.2</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <v>0.34</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="2">
         <v>1.6</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="2">
         <v>2.7</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="2">
         <v>6.2</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="4">
         <v>221</v>
       </c>
-      <c r="L59">
+      <c r="L59" s="2">
         <v>53.8</v>
       </c>
-      <c r="M59">
+      <c r="M59" s="3">
         <v>0.45</v>
       </c>
-      <c r="N59">
+      <c r="N59" s="2">
         <v>6.5</v>
       </c>
-      <c r="O59">
+      <c r="O59" s="2">
         <v>7.6</v>
       </c>
-      <c r="P59">
+      <c r="P59" s="3">
         <v>1.28</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="4">
         <v>3327</v>
       </c>
-      <c r="R59">
+      <c r="R59" s="4">
         <v>305</v>
       </c>
-      <c r="S59">
+      <c r="S59" s="4">
         <v>768</v>
       </c>
-      <c r="T59">
+      <c r="T59" s="2">
         <v>23.1</v>
       </c>
     </row>
@@ -5537,52 +5543,52 @@
       <c r="D60">
         <v>100</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="2">
         <v>8.5</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="2">
         <v>7.2</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <v>0.34</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="2">
         <v>1.4</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="2">
         <v>5.6</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="4">
         <v>121</v>
       </c>
-      <c r="L60">
+      <c r="L60" s="2">
         <v>49.8</v>
       </c>
-      <c r="M60">
+      <c r="M60" s="3">
         <v>0.24</v>
       </c>
-      <c r="N60">
+      <c r="N60" s="2">
         <v>5.3</v>
       </c>
-      <c r="O60">
+      <c r="O60" s="2">
         <v>3.2</v>
       </c>
-      <c r="P60">
+      <c r="P60" s="3">
         <v>0.56000000000000005</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="4">
         <v>3973</v>
       </c>
-      <c r="R60">
+      <c r="R60" s="4">
         <v>270</v>
       </c>
-      <c r="S60">
+      <c r="S60" s="4">
         <v>572</v>
       </c>
-      <c r="T60">
+      <c r="T60" s="2">
         <v>24.9</v>
       </c>
     </row>
@@ -5599,52 +5605,52 @@
       <c r="D61">
         <v>140</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="2">
         <v>7.2</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="3">
         <v>0.3</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="2">
         <v>4.3</v>
       </c>
-      <c r="J61">
+      <c r="J61" s="2">
         <v>5.6</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="4">
         <v>82</v>
       </c>
-      <c r="L61">
+      <c r="L61" s="2">
         <v>43.6</v>
       </c>
-      <c r="M61">
+      <c r="M61" s="3">
         <v>0.17</v>
       </c>
-      <c r="N61">
+      <c r="N61" s="2">
         <v>3.5</v>
       </c>
-      <c r="O61">
+      <c r="O61" s="2">
         <v>1.6</v>
       </c>
-      <c r="P61">
+      <c r="P61" s="3">
         <v>0.28000000000000003</v>
       </c>
-      <c r="Q61">
+      <c r="Q61" s="4">
         <v>4198</v>
       </c>
-      <c r="R61">
+      <c r="R61" s="4">
         <v>233</v>
       </c>
-      <c r="S61">
+      <c r="S61" s="4">
         <v>360</v>
       </c>
-      <c r="T61">
+      <c r="T61" s="2">
         <v>24.7</v>
       </c>
     </row>
@@ -5661,52 +5667,52 @@
       <c r="D62">
         <v>180</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="2">
         <v>8.6</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="2">
         <v>7.2</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="3">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="2">
         <v>1.2</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="2">
         <v>5</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="2">
         <v>5.8</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="4">
         <v>75</v>
       </c>
-      <c r="L62">
+      <c r="L62" s="2">
         <v>35.6</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="3">
         <v>0.17</v>
       </c>
-      <c r="N62">
+      <c r="N62" s="2">
         <v>3.4</v>
       </c>
-      <c r="O62">
+      <c r="O62" s="2">
         <v>1.4</v>
       </c>
-      <c r="P62">
+      <c r="P62" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q62">
+      <c r="Q62" s="4">
         <v>4218</v>
       </c>
-      <c r="R62">
+      <c r="R62" s="4">
         <v>225</v>
       </c>
-      <c r="S62">
+      <c r="S62" s="4">
         <v>314</v>
       </c>
-      <c r="T62">
+      <c r="T62" s="2">
         <v>24.5</v>
       </c>
     </row>

--- a/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_SoilAnalysis.xlsx
+++ b/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2023_F013B4_CO_TILL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5103C3B0-634F-4C30-90B2-39572AEF9731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC3F6FA-84ED-4BDE-BAA8-0EE95A531804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1455" yWindow="-21195" windowWidth="17805" windowHeight="20370" xr2:uid="{429ECE41-D0F7-47CB-8E0A-4F71261A1319}"/>
+    <workbookView xWindow="-1470" yWindow="-28410" windowWidth="17805" windowHeight="20370" xr2:uid="{429ECE41-D0F7-47CB-8E0A-4F71261A1319}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDF" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="330">
   <si>
     <t>Kind Of Sample</t>
   </si>
@@ -1008,14 +1008,18 @@
   </si>
   <si>
     <t>DOY</t>
+  </si>
+  <si>
+    <t>SOIL_DATE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1494,12 +1498,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1875,66 +1880,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F74B010-72C6-43B7-8DFD-502D911BFF79}">
-  <dimension ref="A1:T62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
         <v>297</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>310</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>327</v>
       </c>
@@ -1942,3782 +1950,3966 @@
         <v>328</v>
       </c>
       <c r="C2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D2" t="s">
         <v>297</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>310</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>311</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>312</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>313</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>314</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>315</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>316</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>324</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>317</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>318</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>319</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>320</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>321</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>325</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>322</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>326</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2023</v>
       </c>
       <c r="B3">
         <v>107</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D3" t="s">
         <v>298</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>20</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>8.4</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>7.2</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>0.3</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>1.9</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="2">
         <v>6.9</v>
       </c>
-      <c r="J3" s="2">
+      <c r="K3" s="2">
         <v>7.4</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>328</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="2">
         <v>75.3</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="3">
         <v>1.03</v>
       </c>
-      <c r="N3" s="2">
+      <c r="O3" s="2">
         <v>7</v>
       </c>
-      <c r="O3" s="2">
+      <c r="P3" s="2">
         <v>24.2</v>
       </c>
-      <c r="P3" s="3">
+      <c r="Q3" s="3">
         <v>3.32</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="R3" s="4">
         <v>3137</v>
       </c>
-      <c r="R3" s="4">
+      <c r="S3" s="4">
         <v>264</v>
       </c>
-      <c r="S3" s="4">
+      <c r="T3" s="4">
         <v>541</v>
       </c>
-      <c r="T3" s="2">
+      <c r="U3" s="2">
         <v>21.1</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
       <c r="B4">
         <v>107</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D4" t="s">
         <v>298</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>60</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>8.4</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>7.2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>1.3</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>6.9</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>5.8</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
         <v>199</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
         <v>141.4</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>0.45</v>
       </c>
-      <c r="N4" s="2">
+      <c r="O4" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O4" s="2">
+      <c r="P4" s="2">
         <v>8.6</v>
       </c>
-      <c r="P4" s="3">
+      <c r="Q4" s="3">
         <v>1.73</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="R4" s="4">
         <v>4382</v>
       </c>
-      <c r="R4" s="4">
+      <c r="S4" s="4">
         <v>234</v>
       </c>
-      <c r="S4" s="4">
+      <c r="T4" s="4">
         <v>625</v>
       </c>
-      <c r="T4" s="2">
+      <c r="U4" s="2">
         <v>27.1</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2023</v>
       </c>
       <c r="B5">
         <v>107</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D5" t="s">
         <v>298</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>100</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>7.2</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>1.54</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>1.4</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>30</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <v>5.7</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <v>146</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
         <v>409.4</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>0.19</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O5" s="2">
         <v>4.3</v>
       </c>
-      <c r="O5" s="2">
+      <c r="P5" s="2">
         <v>5.3</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>0.97</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="R5" s="4">
         <v>5092</v>
       </c>
-      <c r="R5" s="4">
+      <c r="S5" s="4">
         <v>268</v>
       </c>
-      <c r="S5" s="4">
+      <c r="T5" s="4">
         <v>910</v>
       </c>
-      <c r="T5" s="2">
+      <c r="U5" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2023</v>
       </c>
       <c r="B6">
         <v>107</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D6" t="s">
         <v>298</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>140</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>7.2</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>0.76</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <v>12.6</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <v>6</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4">
         <v>106</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
         <v>134.80000000000001</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>0.18</v>
       </c>
-      <c r="N6" s="2">
+      <c r="O6" s="2">
         <v>3.6</v>
       </c>
-      <c r="O6" s="2">
+      <c r="P6" s="2">
         <v>3.5</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>0.52</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="R6" s="4">
         <v>5022</v>
       </c>
-      <c r="R6" s="4">
+      <c r="S6" s="4">
         <v>248</v>
       </c>
-      <c r="S6" s="4">
+      <c r="T6" s="4">
         <v>446</v>
       </c>
-      <c r="T6" s="2">
+      <c r="U6" s="2">
         <v>29.4</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2023</v>
       </c>
       <c r="B7">
         <v>107</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D7" t="s">
         <v>298</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>180</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>7.2</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>0.77</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>14.5</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>5.7</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4">
         <v>110</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>141</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>0.2</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>3.7</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>3.6</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>0.54</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="R7" s="4">
         <v>5136</v>
       </c>
-      <c r="R7" s="4">
+      <c r="S7" s="4">
         <v>261</v>
       </c>
-      <c r="S7" s="4">
+      <c r="T7" s="4">
         <v>513</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>30.4</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2023</v>
       </c>
       <c r="B8">
         <v>107</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D8" t="s">
         <v>299</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>20</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="2">
         <v>8.5</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>7.2</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>1.9</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <v>4.3</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <v>6.5</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="4">
         <v>351</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <v>49.6</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1.2</v>
       </c>
-      <c r="N8" s="2">
+      <c r="O8" s="2">
         <v>6.8</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
         <v>23.1</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3.12</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="R8" s="4">
         <v>3441</v>
       </c>
-      <c r="R8" s="4">
+      <c r="S8" s="4">
         <v>255</v>
       </c>
-      <c r="S8" s="4">
+      <c r="T8" s="4">
         <v>469</v>
       </c>
-      <c r="T8" s="2">
+      <c r="U8" s="2">
         <v>22.3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2023</v>
       </c>
       <c r="B9">
         <v>107</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D9" t="s">
         <v>299</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>60</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>8.6</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>7.2</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>0.45</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>1.3</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9" s="2">
         <v>4.5</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <v>5.7</v>
       </c>
-      <c r="K9" s="4">
+      <c r="L9" s="4">
         <v>184</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="2">
         <v>94.2</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>0.51</v>
       </c>
-      <c r="N9" s="2">
+      <c r="O9" s="2">
         <v>6</v>
       </c>
-      <c r="O9" s="2">
+      <c r="P9" s="2">
         <v>9.1</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2.0299999999999998</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="R9" s="4">
         <v>3916</v>
       </c>
-      <c r="R9" s="4">
+      <c r="S9" s="4">
         <v>222</v>
       </c>
-      <c r="S9" s="4">
+      <c r="T9" s="4">
         <v>690</v>
       </c>
-      <c r="T9" s="2">
+      <c r="U9" s="2">
         <v>24.9</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2023</v>
       </c>
       <c r="B10">
         <v>107</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D10" t="s">
         <v>299</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>100</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <v>7.2</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1.17</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>1.5</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="2">
         <v>11</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10" s="2">
         <v>5.7</v>
       </c>
-      <c r="K10" s="4">
+      <c r="L10" s="4">
         <v>145</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
         <v>182</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>0.34</v>
       </c>
-      <c r="N10" s="2">
+      <c r="O10" s="2">
         <v>4.2</v>
       </c>
-      <c r="O10" s="2">
+      <c r="P10" s="2">
         <v>2.8</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>0.73</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="R10" s="4">
         <v>5037</v>
       </c>
-      <c r="R10" s="4">
+      <c r="S10" s="4">
         <v>259</v>
       </c>
-      <c r="S10" s="4">
+      <c r="T10" s="4">
         <v>756</v>
       </c>
-      <c r="T10" s="2">
+      <c r="U10" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2023</v>
       </c>
       <c r="B11">
         <v>107</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D11" t="s">
         <v>299</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>140</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="2">
         <v>8.4</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="2">
         <v>7.2</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>1.3</v>
       </c>
-      <c r="I11" s="2">
+      <c r="J11" s="2">
         <v>3.9</v>
       </c>
-      <c r="J11" s="2">
+      <c r="K11" s="2">
         <v>5.8</v>
       </c>
-      <c r="K11" s="4">
+      <c r="L11" s="4">
         <v>135</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <v>255.9</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>0.3</v>
       </c>
-      <c r="N11" s="2">
+      <c r="O11" s="2">
         <v>4.2</v>
       </c>
-      <c r="O11" s="2">
+      <c r="P11" s="2">
         <v>1.8</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>0.45</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="R11" s="4">
         <v>5295</v>
       </c>
-      <c r="R11" s="4">
+      <c r="S11" s="4">
         <v>272</v>
       </c>
-      <c r="S11" s="4">
+      <c r="T11" s="4">
         <v>721</v>
       </c>
-      <c r="T11" s="2">
+      <c r="U11" s="2">
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2023</v>
       </c>
       <c r="B12">
         <v>107</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D12" t="s">
         <v>299</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>180</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="2">
         <v>8.1</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>7.2</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>0.9</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <v>1</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <v>5.5</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <v>5.6</v>
       </c>
-      <c r="K12" s="4">
+      <c r="L12" s="4">
         <v>84</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <v>153.69999999999999</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>0.47</v>
       </c>
-      <c r="N12" s="2">
+      <c r="O12" s="2">
         <v>3.1</v>
       </c>
-      <c r="O12" s="2">
+      <c r="P12" s="2">
         <v>1.7</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>0.33</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="R12" s="4">
         <v>5226</v>
       </c>
-      <c r="R12" s="4">
+      <c r="S12" s="4">
         <v>246</v>
       </c>
-      <c r="S12" s="4">
+      <c r="T12" s="4">
         <v>404</v>
       </c>
-      <c r="T12" s="2">
+      <c r="U12" s="2">
         <v>30.1</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2023</v>
       </c>
       <c r="B13">
         <v>107</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D13" t="s">
         <v>300</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>20</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <v>7.2</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>1.35</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <v>1.9</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J13" s="2">
         <v>3.7</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <v>7</v>
       </c>
-      <c r="K13" s="4">
+      <c r="L13" s="4">
         <v>358</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="2">
         <v>311.3</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>1.2</v>
       </c>
-      <c r="N13" s="2">
+      <c r="O13" s="2">
         <v>6.9</v>
       </c>
-      <c r="O13" s="2">
+      <c r="P13" s="2">
         <v>22</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3">
         <v>3.54</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="R13" s="4">
         <v>3408</v>
       </c>
-      <c r="R13" s="4">
+      <c r="S13" s="4">
         <v>293</v>
       </c>
-      <c r="S13" s="4">
+      <c r="T13" s="4">
         <v>1063</v>
       </c>
-      <c r="T13" s="2">
+      <c r="U13" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2023</v>
       </c>
       <c r="B14">
         <v>107</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D14" t="s">
         <v>300</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>60</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="2">
         <v>8.1</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <v>7.2</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1.27</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <v>1.5</v>
       </c>
-      <c r="I14" s="2">
+      <c r="J14" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <v>5.9</v>
       </c>
-      <c r="K14" s="4">
+      <c r="L14" s="4">
         <v>253</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
         <v>299.89999999999998</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>0.61</v>
       </c>
-      <c r="N14" s="2">
+      <c r="O14" s="2">
         <v>7</v>
       </c>
-      <c r="O14" s="2">
+      <c r="P14" s="2">
         <v>10.199999999999999</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1.98</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="R14" s="4">
         <v>4549</v>
       </c>
-      <c r="R14" s="4">
+      <c r="S14" s="4">
         <v>348</v>
       </c>
-      <c r="S14" s="4">
+      <c r="T14" s="4">
         <v>1242</v>
       </c>
-      <c r="T14" s="2">
+      <c r="U14" s="2">
         <v>31.7</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
       <c r="B15">
         <v>107</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D15" t="s">
         <v>300</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>100</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="2">
         <v>7.2</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1.46</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <v>1.3</v>
       </c>
-      <c r="I15" s="2">
+      <c r="J15" s="2">
         <v>3</v>
       </c>
-      <c r="J15" s="2">
+      <c r="K15" s="2">
         <v>5.8</v>
       </c>
-      <c r="K15" s="4">
+      <c r="L15" s="4">
         <v>119</v>
       </c>
-      <c r="L15" s="2">
+      <c r="M15" s="2">
         <v>209.8</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>0.48</v>
       </c>
-      <c r="N15" s="2">
+      <c r="O15" s="2">
         <v>4</v>
       </c>
-      <c r="O15" s="2">
+      <c r="P15" s="2">
         <v>4.3</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>0.73</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="R15" s="4">
         <v>5221</v>
       </c>
-      <c r="R15" s="4">
+      <c r="S15" s="4">
         <v>292</v>
       </c>
-      <c r="S15" s="4">
+      <c r="T15" s="4">
         <v>787</v>
       </c>
-      <c r="T15" s="2">
+      <c r="U15" s="2">
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2023</v>
       </c>
       <c r="B16">
         <v>107</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D16" t="s">
         <v>300</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>140</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="2">
         <v>7.2</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>1.05</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I16" s="2">
+      <c r="J16" s="2">
         <v>2.5</v>
       </c>
-      <c r="J16" s="2">
+      <c r="K16" s="2">
         <v>5.5</v>
       </c>
-      <c r="K16" s="4">
+      <c r="L16" s="4">
         <v>70</v>
       </c>
-      <c r="L16" s="2">
+      <c r="M16" s="2">
         <v>157.5</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>0.36</v>
       </c>
-      <c r="N16" s="2">
+      <c r="O16" s="2">
         <v>3.3</v>
       </c>
-      <c r="O16" s="2">
+      <c r="P16" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <v>0.43</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="R16" s="4">
         <v>4846</v>
       </c>
-      <c r="R16" s="4">
+      <c r="S16" s="4">
         <v>235</v>
       </c>
-      <c r="S16" s="4">
+      <c r="T16" s="4">
         <v>387</v>
       </c>
-      <c r="T16" s="2">
+      <c r="U16" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2023</v>
       </c>
       <c r="B17">
         <v>107</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D17" t="s">
         <v>300</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>180</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="2">
         <v>7.2</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>0.93</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>1.2</v>
       </c>
-      <c r="I17" s="2">
+      <c r="J17" s="2">
         <v>1.9</v>
       </c>
-      <c r="J17" s="2">
+      <c r="K17" s="2">
         <v>5.9</v>
       </c>
-      <c r="K17" s="4">
+      <c r="L17" s="4">
         <v>80</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
         <v>95.2</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>0.4</v>
       </c>
-      <c r="N17" s="2">
+      <c r="O17" s="2">
         <v>3.5</v>
       </c>
-      <c r="O17" s="2">
+      <c r="P17" s="2">
         <v>1.4</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="R17" s="4">
         <v>5120</v>
       </c>
-      <c r="R17" s="4">
+      <c r="S17" s="4">
         <v>267</v>
       </c>
-      <c r="S17" s="4">
+      <c r="T17" s="4">
         <v>353</v>
       </c>
-      <c r="T17" s="2">
+      <c r="U17" s="2">
         <v>29.6</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2023</v>
       </c>
       <c r="B18">
         <v>107</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D18" t="s">
         <v>301</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>20</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>8.4</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>7.2</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>0.41</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>1.8</v>
       </c>
-      <c r="I18" s="2">
+      <c r="J18" s="2">
         <v>1.3</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <v>7</v>
       </c>
-      <c r="K18" s="4">
+      <c r="L18" s="4">
         <v>311</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <v>42.4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>0.99</v>
       </c>
-      <c r="N18" s="2">
+      <c r="O18" s="2">
         <v>6.9</v>
       </c>
-      <c r="O18" s="2">
+      <c r="P18" s="2">
         <v>22.7</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3.47</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="R18" s="4">
         <v>3360</v>
       </c>
-      <c r="R18" s="4">
+      <c r="S18" s="4">
         <v>267</v>
       </c>
-      <c r="S18" s="4">
+      <c r="T18" s="4">
         <v>536</v>
       </c>
-      <c r="T18" s="2">
+      <c r="U18" s="2">
         <v>22.2</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2023</v>
       </c>
       <c r="B19">
         <v>107</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D19" t="s">
         <v>301</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>60</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="2">
         <v>8.6</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="2">
         <v>7.2</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>0.7</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>1.2</v>
       </c>
-      <c r="I19" s="2">
+      <c r="J19" s="2">
         <v>2.7</v>
       </c>
-      <c r="J19" s="2">
+      <c r="K19" s="2">
         <v>5.9</v>
       </c>
-      <c r="K19" s="4">
+      <c r="L19" s="4">
         <v>198</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="2">
         <v>117.9</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>0.25</v>
       </c>
-      <c r="N19" s="2">
+      <c r="O19" s="2">
         <v>5.3</v>
       </c>
-      <c r="O19" s="2">
+      <c r="P19" s="2">
         <v>7.9</v>
       </c>
-      <c r="P19" s="3">
+      <c r="Q19" s="3">
         <v>1.68</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="R19" s="4">
         <v>3833</v>
       </c>
-      <c r="R19" s="4">
+      <c r="S19" s="4">
         <v>232</v>
       </c>
-      <c r="S19" s="4">
+      <c r="T19" s="4">
         <v>677</v>
       </c>
-      <c r="T19" s="2">
+      <c r="U19" s="2">
         <v>24.5</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2023</v>
       </c>
       <c r="B20">
         <v>107</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D20" t="s">
         <v>301</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>100</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F20" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="2">
         <v>7.2</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1.33</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>1.3</v>
       </c>
-      <c r="I20" s="2">
+      <c r="J20" s="2">
         <v>6.1</v>
       </c>
-      <c r="J20" s="2">
+      <c r="K20" s="2">
         <v>5.7</v>
       </c>
-      <c r="K20" s="4">
+      <c r="L20" s="4">
         <v>117</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
         <v>205.9</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>0.16</v>
       </c>
-      <c r="N20" s="2">
+      <c r="O20" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O20" s="2">
+      <c r="P20" s="2">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>0.76</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="R20" s="4">
         <v>4605</v>
       </c>
-      <c r="R20" s="4">
+      <c r="S20" s="4">
         <v>235</v>
       </c>
-      <c r="S20" s="4">
+      <c r="T20" s="4">
         <v>746</v>
       </c>
-      <c r="T20" s="2">
+      <c r="U20" s="2">
         <v>28.5</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2023</v>
       </c>
       <c r="B21">
         <v>107</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D21" t="s">
         <v>301</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>140</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <v>7.2</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1.39</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <v>1.2</v>
-      </c>
-      <c r="I21" s="2">
-        <v>6.2</v>
       </c>
       <c r="J21" s="2">
         <v>6.2</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="L21" s="4">
         <v>89</v>
       </c>
-      <c r="L21" s="2">
+      <c r="M21" s="2">
         <v>265.2</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="N21" s="2">
+      <c r="O21" s="2">
         <v>3.7</v>
       </c>
-      <c r="O21" s="2">
+      <c r="P21" s="2">
         <v>2.5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>0.5</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="R21" s="4">
         <v>4610</v>
       </c>
-      <c r="R21" s="4">
+      <c r="S21" s="4">
         <v>241</v>
       </c>
-      <c r="S21" s="4">
+      <c r="T21" s="4">
         <v>487</v>
       </c>
-      <c r="T21" s="2">
+      <c r="U21" s="2">
         <v>27.4</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2023</v>
       </c>
       <c r="B22">
         <v>107</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D22" t="s">
         <v>301</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>180</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="2">
         <v>8.4</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="2">
         <v>7.2</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>0.84</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <v>1</v>
       </c>
-      <c r="I22" s="2">
+      <c r="J22" s="2">
         <v>3.4</v>
       </c>
-      <c r="J22" s="2">
+      <c r="K22" s="2">
         <v>5</v>
       </c>
-      <c r="K22" s="4">
+      <c r="L22" s="4">
         <v>74</v>
       </c>
-      <c r="L22" s="2">
+      <c r="M22" s="2">
         <v>103.9</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>0.19</v>
       </c>
-      <c r="N22" s="2">
+      <c r="O22" s="2">
         <v>3.9</v>
       </c>
-      <c r="O22" s="2">
+      <c r="P22" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>0.36</v>
       </c>
-      <c r="Q22" s="4">
+      <c r="R22" s="4">
         <v>4426</v>
       </c>
-      <c r="R22" s="4">
+      <c r="S22" s="4">
         <v>202</v>
       </c>
-      <c r="S22" s="4">
+      <c r="T22" s="4">
         <v>324</v>
       </c>
-      <c r="T22" s="2">
+      <c r="U22" s="2">
         <v>25.4</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2023</v>
       </c>
       <c r="B23">
         <v>107</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D23" t="s">
         <v>302</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>20</v>
       </c>
-      <c r="E23" s="2">
+      <c r="F23" s="2">
         <v>8.5</v>
       </c>
-      <c r="F23" s="2">
+      <c r="G23" s="2">
         <v>7.2</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>0.52</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <v>2</v>
       </c>
-      <c r="I23" s="2">
+      <c r="J23" s="2">
         <v>3.1</v>
       </c>
-      <c r="J23" s="2">
+      <c r="K23" s="2">
         <v>6.3</v>
       </c>
-      <c r="K23" s="4">
+      <c r="L23" s="4">
         <v>268</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="2">
         <v>56.2</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1.2</v>
       </c>
-      <c r="N23" s="2">
+      <c r="O23" s="2">
         <v>6.3</v>
       </c>
-      <c r="O23" s="2">
+      <c r="P23" s="2">
         <v>17.8</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3.48</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="R23" s="4">
         <v>2350</v>
       </c>
-      <c r="R23" s="4">
+      <c r="S23" s="4">
         <v>207</v>
       </c>
-      <c r="S23" s="4">
+      <c r="T23" s="4">
         <v>400</v>
       </c>
-      <c r="T23" s="2">
+      <c r="U23" s="2">
         <v>15.9</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2023</v>
       </c>
       <c r="B24">
         <v>107</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D24" t="s">
         <v>302</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>60</v>
       </c>
-      <c r="E24" s="2">
+      <c r="F24" s="2">
         <v>8.4</v>
       </c>
-      <c r="F24" s="2">
+      <c r="G24" s="2">
         <v>7.2</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1.01</v>
       </c>
-      <c r="H24" s="2">
+      <c r="I24" s="2">
         <v>1.4</v>
       </c>
-      <c r="I24" s="2">
+      <c r="J24" s="2">
         <v>8.1</v>
       </c>
-      <c r="J24" s="2">
+      <c r="K24" s="2">
         <v>5.9</v>
       </c>
-      <c r="K24" s="4">
+      <c r="L24" s="4">
         <v>164</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="2">
         <v>121.4</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>0.65</v>
       </c>
-      <c r="N24" s="2">
+      <c r="O24" s="2">
         <v>4.3</v>
       </c>
-      <c r="O24" s="2">
+      <c r="P24" s="2">
         <v>6.3</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1.72</v>
       </c>
-      <c r="Q24" s="4">
+      <c r="R24" s="4">
         <v>3628</v>
       </c>
-      <c r="R24" s="4">
+      <c r="S24" s="4">
         <v>261</v>
       </c>
-      <c r="S24" s="4">
+      <c r="T24" s="4">
         <v>576</v>
       </c>
-      <c r="T24" s="2">
+      <c r="U24" s="2">
         <v>23.2</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2023</v>
       </c>
       <c r="B25">
         <v>107</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D25" t="s">
         <v>302</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>100</v>
       </c>
-      <c r="E25" s="2">
+      <c r="F25" s="2">
         <v>8.4</v>
       </c>
-      <c r="F25" s="2">
+      <c r="G25" s="2">
         <v>7.2</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H25" s="3">
         <v>0.96</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="2">
         <v>1</v>
       </c>
-      <c r="I25" s="2">
+      <c r="J25" s="2">
         <v>7.9</v>
       </c>
-      <c r="J25" s="2">
+      <c r="K25" s="2">
         <v>6</v>
       </c>
-      <c r="K25" s="4">
+      <c r="L25" s="4">
         <v>136</v>
       </c>
-      <c r="L25" s="2">
+      <c r="M25" s="2">
         <v>171.5</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N25" s="3">
         <v>0.74</v>
       </c>
-      <c r="N25" s="2">
+      <c r="O25" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O25" s="2">
+      <c r="P25" s="2">
         <v>4.8</v>
       </c>
-      <c r="P25" s="3">
+      <c r="Q25" s="3">
         <v>0.74</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="R25" s="4">
         <v>3734</v>
       </c>
-      <c r="R25" s="4">
+      <c r="S25" s="4">
         <v>218</v>
       </c>
-      <c r="S25" s="4">
+      <c r="T25" s="4">
         <v>786</v>
       </c>
-      <c r="T25" s="2">
+      <c r="U25" s="2">
         <v>24.3</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2023</v>
       </c>
       <c r="B26">
         <v>107</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D26" t="s">
         <v>302</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>140</v>
       </c>
-      <c r="E26" s="2">
+      <c r="F26" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F26" s="2">
+      <c r="G26" s="2">
         <v>7.2</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1.04</v>
       </c>
-      <c r="H26" s="2">
+      <c r="I26" s="2">
         <v>1.2</v>
       </c>
-      <c r="I26" s="2">
+      <c r="J26" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J26" s="2">
+      <c r="K26" s="2">
         <v>5.5</v>
       </c>
-      <c r="K26" s="4">
+      <c r="L26" s="4">
         <v>116</v>
       </c>
-      <c r="L26" s="2">
+      <c r="M26" s="2">
         <v>259.10000000000002</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>0.46</v>
       </c>
-      <c r="N26" s="2">
+      <c r="O26" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O26" s="2">
+      <c r="P26" s="2">
         <v>3.7</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>0.75</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="R26" s="4">
         <v>4158</v>
       </c>
-      <c r="R26" s="4">
+      <c r="S26" s="4">
         <v>226</v>
       </c>
-      <c r="S26" s="4">
+      <c r="T26" s="4">
         <v>551</v>
       </c>
-      <c r="T26" s="2">
+      <c r="U26" s="2">
         <v>25.4</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2023</v>
       </c>
       <c r="B27">
         <v>107</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D27" t="s">
         <v>302</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>180</v>
       </c>
-      <c r="E27" s="2">
+      <c r="F27" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F27" s="2">
+      <c r="G27" s="2">
         <v>7.2</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>0.94</v>
       </c>
-      <c r="H27" s="2">
+      <c r="I27" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I27" s="2">
+      <c r="J27" s="2">
         <v>2.5</v>
       </c>
-      <c r="J27" s="2">
+      <c r="K27" s="2">
         <v>6.2</v>
       </c>
-      <c r="K27" s="4">
+      <c r="L27" s="4">
         <v>89</v>
       </c>
-      <c r="L27" s="2">
+      <c r="M27" s="2">
         <v>91.1</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>0.69</v>
       </c>
-      <c r="N27" s="2">
+      <c r="O27" s="2">
         <v>4.3</v>
       </c>
-      <c r="O27" s="2">
+      <c r="P27" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>0.54</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="R27" s="4">
         <v>4563</v>
       </c>
-      <c r="R27" s="4">
+      <c r="S27" s="4">
         <v>236</v>
       </c>
-      <c r="S27" s="4">
+      <c r="T27" s="4">
         <v>384</v>
       </c>
-      <c r="T27" s="2">
+      <c r="U27" s="2">
         <v>26.7</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2023</v>
       </c>
       <c r="B28">
         <v>107</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D28" t="s">
         <v>303</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>20</v>
       </c>
-      <c r="E28" s="2">
+      <c r="F28" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F28" s="2">
+      <c r="G28" s="2">
         <v>7.2</v>
       </c>
-      <c r="G28" s="3">
+      <c r="H28" s="3">
         <v>0.9</v>
       </c>
-      <c r="H28" s="2">
+      <c r="I28" s="2">
         <v>1.8</v>
       </c>
-      <c r="I28" s="2">
+      <c r="J28" s="2">
         <v>3.7</v>
       </c>
-      <c r="J28" s="2">
+      <c r="K28" s="2">
         <v>7.2</v>
       </c>
-      <c r="K28" s="4">
+      <c r="L28" s="4">
         <v>325</v>
       </c>
-      <c r="L28" s="2">
+      <c r="M28" s="2">
         <v>148</v>
       </c>
-      <c r="M28" s="3">
+      <c r="N28" s="3">
         <v>1.03</v>
       </c>
-      <c r="N28" s="2">
+      <c r="O28" s="2">
         <v>6.9</v>
       </c>
-      <c r="O28" s="2">
+      <c r="P28" s="2">
         <v>24.1</v>
       </c>
-      <c r="P28" s="3">
+      <c r="Q28" s="3">
         <v>3.27</v>
       </c>
-      <c r="Q28" s="4">
+      <c r="R28" s="4">
         <v>3173</v>
       </c>
-      <c r="R28" s="4">
+      <c r="S28" s="4">
         <v>235</v>
       </c>
-      <c r="S28" s="4">
+      <c r="T28" s="4">
         <v>542</v>
       </c>
-      <c r="T28" s="2">
+      <c r="U28" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2023</v>
       </c>
       <c r="B29">
         <v>107</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D29" t="s">
         <v>303</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>60</v>
       </c>
-      <c r="E29" s="2">
+      <c r="F29" s="2">
         <v>8.4</v>
       </c>
-      <c r="F29" s="2">
+      <c r="G29" s="2">
         <v>7.2</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>1.25</v>
       </c>
-      <c r="H29" s="2">
+      <c r="I29" s="2">
         <v>1.5</v>
       </c>
-      <c r="I29" s="2">
+      <c r="J29" s="2">
         <v>10.9</v>
       </c>
-      <c r="J29" s="2">
+      <c r="K29" s="2">
         <v>6.2</v>
       </c>
-      <c r="K29" s="4">
+      <c r="L29" s="4">
         <v>197</v>
       </c>
-      <c r="L29" s="2">
+      <c r="M29" s="2">
         <v>146.4</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N29" s="2">
+      <c r="O29" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O29" s="2">
+      <c r="P29" s="2">
         <v>9.5</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1.58</v>
       </c>
-      <c r="Q29" s="4">
+      <c r="R29" s="4">
         <v>4574</v>
       </c>
-      <c r="R29" s="4">
+      <c r="S29" s="4">
         <v>264</v>
       </c>
-      <c r="S29" s="4">
+      <c r="T29" s="4">
         <v>913</v>
       </c>
-      <c r="T29" s="2">
+      <c r="U29" s="2">
         <v>29.5</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2023</v>
       </c>
       <c r="B30">
         <v>107</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D30" t="s">
         <v>303</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>100</v>
       </c>
-      <c r="E30" s="2">
+      <c r="F30" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F30" s="2">
+      <c r="G30" s="2">
         <v>7.2</v>
       </c>
-      <c r="G30" s="3">
+      <c r="H30" s="3">
         <v>1.38</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="2">
         <v>1.5</v>
       </c>
-      <c r="I30" s="2">
+      <c r="J30" s="2">
         <v>4.3</v>
       </c>
-      <c r="J30" s="2">
+      <c r="K30" s="2">
         <v>6</v>
       </c>
-      <c r="K30" s="4">
+      <c r="L30" s="4">
         <v>128</v>
       </c>
-      <c r="L30" s="2">
+      <c r="M30" s="2">
         <v>228.1</v>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <v>0.25</v>
       </c>
-      <c r="N30" s="2">
+      <c r="O30" s="2">
         <v>4.3</v>
       </c>
-      <c r="O30" s="2">
+      <c r="P30" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P30" s="3">
+      <c r="Q30" s="3">
         <v>0.8</v>
       </c>
-      <c r="Q30" s="4">
+      <c r="R30" s="4">
         <v>4907</v>
       </c>
-      <c r="R30" s="4">
+      <c r="S30" s="4">
         <v>277</v>
       </c>
-      <c r="S30" s="4">
+      <c r="T30" s="4">
         <v>755</v>
       </c>
-      <c r="T30" s="2">
+      <c r="U30" s="2">
         <v>30.5</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2023</v>
       </c>
       <c r="B31">
         <v>107</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D31" t="s">
         <v>303</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>140</v>
       </c>
-      <c r="E31" s="2">
+      <c r="F31" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F31" s="2">
+      <c r="G31" s="2">
         <v>7.2</v>
       </c>
-      <c r="G31" s="3">
+      <c r="H31" s="3">
         <v>1.2</v>
       </c>
-      <c r="H31" s="2">
+      <c r="I31" s="2">
         <v>1.2</v>
       </c>
-      <c r="I31" s="2">
+      <c r="J31" s="2">
         <v>1.9</v>
       </c>
-      <c r="J31" s="2">
+      <c r="K31" s="2">
         <v>5.6</v>
       </c>
-      <c r="K31" s="4">
+      <c r="L31" s="4">
         <v>89</v>
       </c>
-      <c r="L31" s="2">
+      <c r="M31" s="2">
         <v>110.5</v>
       </c>
-      <c r="M31" s="3">
+      <c r="N31" s="3">
         <v>0.12</v>
       </c>
-      <c r="N31" s="2">
+      <c r="O31" s="2">
         <v>3.4</v>
       </c>
-      <c r="O31" s="2">
+      <c r="P31" s="2">
         <v>1.7</v>
       </c>
-      <c r="P31" s="3">
+      <c r="Q31" s="3">
         <v>0.43</v>
       </c>
-      <c r="Q31" s="4">
+      <c r="R31" s="4">
         <v>4716</v>
       </c>
-      <c r="R31" s="4">
+      <c r="S31" s="4">
         <v>267</v>
       </c>
-      <c r="S31" s="4">
+      <c r="T31" s="4">
         <v>436</v>
       </c>
-      <c r="T31" s="2">
+      <c r="U31" s="2">
         <v>27.9</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2023</v>
       </c>
       <c r="B32">
         <v>107</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="5">
+        <v>45033</v>
+      </c>
+      <c r="D32" t="s">
         <v>303</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>180</v>
       </c>
-      <c r="E32" s="2">
+      <c r="F32" s="2">
         <v>8.5</v>
       </c>
-      <c r="F32" s="2">
+      <c r="G32" s="2">
         <v>7.2</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>0.54</v>
       </c>
-      <c r="H32" s="2">
+      <c r="I32" s="2">
         <v>1</v>
       </c>
-      <c r="I32" s="2">
+      <c r="J32" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J32" s="2">
+      <c r="K32" s="2">
         <v>6.1</v>
       </c>
-      <c r="K32" s="4">
+      <c r="L32" s="4">
         <v>101</v>
       </c>
-      <c r="L32" s="2">
+      <c r="M32" s="2">
         <v>60.8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>0.24</v>
       </c>
-      <c r="N32" s="2">
+      <c r="O32" s="2">
         <v>3.4</v>
       </c>
-      <c r="O32" s="2">
+      <c r="P32" s="2">
         <v>3.9</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>0.67</v>
       </c>
-      <c r="Q32" s="4">
+      <c r="R32" s="4">
         <v>4224</v>
       </c>
-      <c r="R32" s="4">
+      <c r="S32" s="4">
         <v>231</v>
       </c>
-      <c r="S32" s="4">
+      <c r="T32" s="4">
         <v>282</v>
       </c>
-      <c r="T32" s="2">
+      <c r="U32" s="2">
         <v>24.5</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2023</v>
       </c>
       <c r="B33">
         <v>114</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D33" t="s">
         <v>304</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>20</v>
       </c>
-      <c r="E33" s="2">
+      <c r="F33" s="2">
         <v>8.5</v>
       </c>
-      <c r="F33" s="2">
+      <c r="G33" s="2">
         <v>7.2</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>0.84</v>
       </c>
-      <c r="H33" s="2">
+      <c r="I33" s="2">
         <v>1.8</v>
       </c>
-      <c r="I33" s="2">
+      <c r="J33" s="2">
         <v>3.6</v>
       </c>
-      <c r="J33" s="2">
+      <c r="K33" s="2">
         <v>5.9</v>
       </c>
-      <c r="K33" s="4">
+      <c r="L33" s="4">
         <v>258</v>
       </c>
-      <c r="L33" s="2">
+      <c r="M33" s="2">
         <v>89.4</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>0.6</v>
       </c>
-      <c r="N33" s="2">
+      <c r="O33" s="2">
         <v>3.6</v>
       </c>
-      <c r="O33" s="2">
+      <c r="P33" s="2">
         <v>5.9</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2</v>
       </c>
-      <c r="Q33" s="4">
+      <c r="R33" s="4">
         <v>4025</v>
       </c>
-      <c r="R33" s="4">
+      <c r="S33" s="4">
         <v>285</v>
       </c>
-      <c r="S33" s="4">
+      <c r="T33" s="4">
         <v>652</v>
       </c>
-      <c r="T33" s="2">
+      <c r="U33" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2023</v>
       </c>
       <c r="B34">
         <v>114</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D34" t="s">
         <v>304</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>60</v>
       </c>
-      <c r="E34" s="2">
+      <c r="F34" s="2">
         <v>8.5</v>
       </c>
-      <c r="F34" s="2">
+      <c r="G34" s="2">
         <v>7.2</v>
       </c>
-      <c r="G34" s="3">
+      <c r="H34" s="3">
         <v>0.84</v>
       </c>
-      <c r="H34" s="2">
+      <c r="I34" s="2">
         <v>1.4</v>
       </c>
-      <c r="I34" s="2">
+      <c r="J34" s="2">
         <v>2</v>
       </c>
-      <c r="J34" s="2">
+      <c r="K34" s="2">
         <v>5.9</v>
       </c>
-      <c r="K34" s="4">
+      <c r="L34" s="4">
         <v>150</v>
       </c>
-      <c r="L34" s="2">
+      <c r="M34" s="2">
         <v>87.3</v>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N34" s="2">
+      <c r="O34" s="2">
         <v>3.8</v>
       </c>
-      <c r="O34" s="2">
+      <c r="P34" s="2">
         <v>6.2</v>
       </c>
-      <c r="P34" s="3">
+      <c r="Q34" s="3">
         <v>1.25</v>
       </c>
-      <c r="Q34" s="4">
+      <c r="R34" s="4">
         <v>4746</v>
       </c>
-      <c r="R34" s="4">
+      <c r="S34" s="4">
         <v>240</v>
       </c>
-      <c r="S34" s="4">
+      <c r="T34" s="4">
         <v>717</v>
       </c>
-      <c r="T34" s="2">
+      <c r="U34" s="2">
         <v>29.2</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2023</v>
       </c>
       <c r="B35">
         <v>114</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D35" t="s">
         <v>304</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>100</v>
       </c>
-      <c r="E35" s="2">
+      <c r="F35" s="2">
         <v>8.4</v>
       </c>
-      <c r="F35" s="2">
+      <c r="G35" s="2">
         <v>7.2</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>0.9</v>
       </c>
-      <c r="H35" s="2">
+      <c r="I35" s="2">
         <v>1.5</v>
       </c>
-      <c r="I35" s="2">
+      <c r="J35" s="2">
         <v>3.3</v>
       </c>
-      <c r="J35" s="2">
+      <c r="K35" s="2">
         <v>5.6</v>
       </c>
-      <c r="K35" s="4">
+      <c r="L35" s="4">
         <v>109</v>
       </c>
-      <c r="L35" s="2">
+      <c r="M35" s="2">
         <v>178.6</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>0.11</v>
       </c>
-      <c r="N35" s="2">
+      <c r="O35" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O35" s="2">
+      <c r="P35" s="2">
         <v>1.8</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>0.53</v>
       </c>
-      <c r="Q35" s="4">
+      <c r="R35" s="4">
         <v>4860</v>
       </c>
-      <c r="R35" s="4">
+      <c r="S35" s="4">
         <v>284</v>
       </c>
-      <c r="S35" s="4">
+      <c r="T35" s="4">
         <v>674</v>
       </c>
-      <c r="T35" s="2">
+      <c r="U35" s="2">
         <v>29.9</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2023</v>
       </c>
       <c r="B36">
         <v>114</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D36" t="s">
         <v>304</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>140</v>
       </c>
-      <c r="E36" s="2">
+      <c r="F36" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F36" s="2">
+      <c r="G36" s="2">
         <v>7.2</v>
       </c>
-      <c r="G36" s="3">
+      <c r="H36" s="3">
         <v>0.69</v>
       </c>
-      <c r="H36" s="2">
+      <c r="I36" s="2">
         <v>1.2</v>
       </c>
-      <c r="I36" s="2">
+      <c r="J36" s="2">
         <v>3.7</v>
       </c>
-      <c r="J36" s="2">
+      <c r="K36" s="2">
         <v>5.9</v>
       </c>
-      <c r="K36" s="4">
+      <c r="L36" s="4">
         <v>95</v>
       </c>
-      <c r="L36" s="2">
+      <c r="M36" s="2">
         <v>131.9</v>
       </c>
-      <c r="M36" s="3">
+      <c r="N36" s="3">
         <v>0.16</v>
       </c>
-      <c r="N36" s="2">
+      <c r="O36" s="2">
         <v>3.6</v>
       </c>
-      <c r="O36" s="2">
+      <c r="P36" s="2">
         <v>1.4</v>
       </c>
-      <c r="P36" s="3">
+      <c r="Q36" s="3">
         <v>0.37</v>
       </c>
-      <c r="Q36" s="4">
+      <c r="R36" s="4">
         <v>4784</v>
       </c>
-      <c r="R36" s="4">
+      <c r="S36" s="4">
         <v>278</v>
       </c>
-      <c r="S36" s="4">
+      <c r="T36" s="4">
         <v>491</v>
       </c>
-      <c r="T36" s="2">
+      <c r="U36" s="2">
         <v>28.6</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2023</v>
       </c>
       <c r="B37">
         <v>114</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D37" t="s">
         <v>304</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>180</v>
       </c>
-      <c r="E37" s="2">
+      <c r="F37" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F37" s="2">
+      <c r="G37" s="2">
         <v>7.2</v>
       </c>
-      <c r="G37" s="3">
+      <c r="H37" s="3">
         <v>0.63</v>
       </c>
-      <c r="H37" s="2">
+      <c r="I37" s="2">
         <v>1</v>
       </c>
-      <c r="I37" s="2">
+      <c r="J37" s="2">
         <v>3.7</v>
       </c>
-      <c r="J37" s="2">
+      <c r="K37" s="2">
         <v>5.8</v>
       </c>
-      <c r="K37" s="4">
+      <c r="L37" s="4">
         <v>72</v>
       </c>
-      <c r="L37" s="2">
+      <c r="M37" s="2">
         <v>83.7</v>
       </c>
-      <c r="M37" s="3">
+      <c r="N37" s="3">
         <v>0.34</v>
       </c>
-      <c r="N37" s="2">
+      <c r="O37" s="2">
         <v>3.9</v>
       </c>
-      <c r="O37" s="2">
+      <c r="P37" s="2">
         <v>1.5</v>
       </c>
-      <c r="P37" s="3">
+      <c r="Q37" s="3">
         <v>0.39</v>
       </c>
-      <c r="Q37" s="4">
+      <c r="R37" s="4">
         <v>4307</v>
       </c>
-      <c r="R37" s="4">
+      <c r="S37" s="4">
         <v>213</v>
       </c>
-      <c r="S37" s="4">
+      <c r="T37" s="4">
         <v>288</v>
       </c>
-      <c r="T37" s="2">
+      <c r="U37" s="2">
         <v>24.7</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2023</v>
       </c>
       <c r="B38">
         <v>114</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D38" t="s">
         <v>305</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>20</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>7.2</v>
       </c>
-      <c r="G38" s="3">
+      <c r="H38" s="3">
         <v>0.3</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>1.7</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>3.9</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>6.9</v>
       </c>
-      <c r="K38" s="4">
+      <c r="L38" s="4">
         <v>263</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>25</v>
       </c>
-      <c r="M38" s="3">
+      <c r="N38" s="3">
         <v>1.05</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>5.4</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>14.1</v>
       </c>
-      <c r="P38" s="3">
+      <c r="Q38" s="3">
         <v>2.93</v>
       </c>
-      <c r="Q38" s="4">
+      <c r="R38" s="4">
         <v>2101</v>
       </c>
-      <c r="R38" s="4">
+      <c r="S38" s="4">
         <v>203</v>
       </c>
-      <c r="S38" s="4">
+      <c r="T38" s="4">
         <v>295</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>14.2</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2023</v>
       </c>
       <c r="B39">
         <v>114</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D39" t="s">
         <v>305</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>60</v>
       </c>
-      <c r="E39" s="2">
+      <c r="F39" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F39" s="2">
+      <c r="G39" s="2">
         <v>7.2</v>
       </c>
-      <c r="G39" s="3">
+      <c r="H39" s="3">
         <v>0.32</v>
       </c>
-      <c r="H39" s="2">
+      <c r="I39" s="2">
         <v>1.2</v>
       </c>
-      <c r="I39" s="2">
+      <c r="J39" s="2">
         <v>0.9</v>
       </c>
-      <c r="J39" s="2">
+      <c r="K39" s="2">
         <v>6</v>
       </c>
-      <c r="K39" s="4">
+      <c r="L39" s="4">
         <v>192</v>
       </c>
-      <c r="L39" s="2">
+      <c r="M39" s="2">
         <v>46.6</v>
       </c>
-      <c r="M39" s="3">
+      <c r="N39" s="3">
         <v>0.31</v>
       </c>
-      <c r="N39" s="2">
+      <c r="O39" s="2">
         <v>5.2</v>
       </c>
-      <c r="O39" s="2">
+      <c r="P39" s="2">
         <v>8.4</v>
       </c>
-      <c r="P39" s="3">
+      <c r="Q39" s="3">
         <v>1.59</v>
       </c>
-      <c r="Q39" s="4">
+      <c r="R39" s="4">
         <v>2366</v>
       </c>
-      <c r="R39" s="4">
+      <c r="S39" s="4">
         <v>227</v>
       </c>
-      <c r="S39" s="4">
+      <c r="T39" s="4">
         <v>518</v>
       </c>
-      <c r="T39" s="2">
+      <c r="U39" s="2">
         <v>16.5</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2023</v>
       </c>
       <c r="B40">
         <v>114</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D40" t="s">
         <v>305</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>100</v>
       </c>
-      <c r="E40" s="2">
+      <c r="F40" s="2">
         <v>8.5</v>
       </c>
-      <c r="F40" s="2">
+      <c r="G40" s="2">
         <v>7.2</v>
       </c>
-      <c r="G40" s="3">
+      <c r="H40" s="3">
         <v>0.47</v>
       </c>
-      <c r="H40" s="2">
+      <c r="I40" s="2">
         <v>1</v>
       </c>
-      <c r="I40" s="2">
+      <c r="J40" s="2">
         <v>2.7</v>
       </c>
-      <c r="J40" s="2">
+      <c r="K40" s="2">
         <v>5.7</v>
       </c>
-      <c r="K40" s="4">
+      <c r="L40" s="4">
         <v>130</v>
       </c>
-      <c r="L40" s="2">
+      <c r="M40" s="2">
         <v>66.599999999999994</v>
       </c>
-      <c r="M40" s="3">
+      <c r="N40" s="3">
         <v>0.19</v>
       </c>
-      <c r="N40" s="2">
+      <c r="O40" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="O40" s="2">
+      <c r="P40" s="2">
         <v>4.5</v>
       </c>
-      <c r="P40" s="3">
+      <c r="Q40" s="3">
         <v>0.85</v>
       </c>
-      <c r="Q40" s="4">
+      <c r="R40" s="4">
         <v>3427</v>
       </c>
-      <c r="R40" s="4">
+      <c r="S40" s="4">
         <v>188</v>
       </c>
-      <c r="S40" s="4">
+      <c r="T40" s="4">
         <v>464</v>
       </c>
-      <c r="T40" s="2">
+      <c r="U40" s="2">
         <v>21.1</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2023</v>
       </c>
       <c r="B41">
         <v>114</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D41" t="s">
         <v>305</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>140</v>
       </c>
-      <c r="E41" s="2">
+      <c r="F41" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F41" s="2">
+      <c r="G41" s="2">
         <v>7.2</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>0.68</v>
       </c>
-      <c r="H41" s="2">
+      <c r="I41" s="2">
         <v>1</v>
       </c>
-      <c r="I41" s="2">
+      <c r="J41" s="2">
         <v>3.2</v>
       </c>
-      <c r="J41" s="2">
+      <c r="K41" s="2">
         <v>6.2</v>
       </c>
-      <c r="K41" s="4">
+      <c r="L41" s="4">
         <v>138</v>
       </c>
-      <c r="L41" s="2">
+      <c r="M41" s="2">
         <v>113.7</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>0.27</v>
       </c>
-      <c r="N41" s="2">
+      <c r="O41" s="2">
         <v>4</v>
       </c>
-      <c r="O41" s="2">
+      <c r="P41" s="2">
         <v>2.9</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>0.52</v>
       </c>
-      <c r="Q41" s="4">
+      <c r="R41" s="4">
         <v>4426</v>
       </c>
-      <c r="R41" s="4">
+      <c r="S41" s="4">
         <v>204</v>
       </c>
-      <c r="S41" s="4">
+      <c r="T41" s="4">
         <v>694</v>
       </c>
-      <c r="T41" s="2">
+      <c r="U41" s="2">
         <v>27.2</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2023</v>
       </c>
       <c r="B42">
         <v>114</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D42" t="s">
         <v>305</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>180</v>
       </c>
-      <c r="E42" s="2">
+      <c r="F42" s="2">
         <v>8.1</v>
       </c>
-      <c r="F42" s="2">
+      <c r="G42" s="2">
         <v>7.2</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>0.71</v>
       </c>
-      <c r="H42" s="2">
+      <c r="I42" s="2">
         <v>1.2</v>
       </c>
-      <c r="I42" s="2">
+      <c r="J42" s="2">
         <v>6.1</v>
       </c>
-      <c r="J42" s="2">
+      <c r="K42" s="2">
         <v>5.6</v>
       </c>
-      <c r="K42" s="4">
+      <c r="L42" s="4">
         <v>116</v>
       </c>
-      <c r="L42" s="2">
+      <c r="M42" s="2">
         <v>187.8</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>0.24</v>
       </c>
-      <c r="N42" s="2">
+      <c r="O42" s="2">
         <v>4.3</v>
       </c>
-      <c r="O42" s="2">
+      <c r="P42" s="2">
         <v>3.2</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>0.5</v>
       </c>
-      <c r="Q42" s="4">
+      <c r="R42" s="4">
         <v>4697</v>
       </c>
-      <c r="R42" s="4">
+      <c r="S42" s="4">
         <v>214</v>
       </c>
-      <c r="S42" s="4">
+      <c r="T42" s="4">
         <v>525</v>
       </c>
-      <c r="T42" s="2">
+      <c r="U42" s="2">
         <v>27.9</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2023</v>
       </c>
       <c r="B43">
         <v>114</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D43" t="s">
         <v>306</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>20</v>
       </c>
-      <c r="E43" s="2">
+      <c r="F43" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F43" s="2">
+      <c r="G43" s="2">
         <v>7.2</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>0.34</v>
       </c>
-      <c r="H43" s="2">
+      <c r="I43" s="2">
         <v>1.9</v>
       </c>
-      <c r="I43" s="2">
+      <c r="J43" s="2">
         <v>2.6</v>
       </c>
-      <c r="J43" s="2">
+      <c r="K43" s="2">
         <v>6.7</v>
       </c>
-      <c r="K43" s="4">
+      <c r="L43" s="4">
         <v>342</v>
       </c>
-      <c r="L43" s="2">
+      <c r="M43" s="2">
         <v>42</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1.05</v>
       </c>
-      <c r="N43" s="2">
+      <c r="O43" s="2">
         <v>5.7</v>
       </c>
-      <c r="O43" s="2">
+      <c r="P43" s="2">
         <v>18</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3.09</v>
       </c>
-      <c r="Q43" s="4">
+      <c r="R43" s="4">
         <v>2666</v>
       </c>
-      <c r="R43" s="4">
+      <c r="S43" s="4">
         <v>257</v>
       </c>
-      <c r="S43" s="4">
+      <c r="T43" s="4">
         <v>448</v>
       </c>
-      <c r="T43" s="2">
+      <c r="U43" s="2">
         <v>18.3</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2023</v>
       </c>
       <c r="B44">
         <v>114</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D44" t="s">
         <v>306</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>60</v>
       </c>
-      <c r="E44" s="2">
+      <c r="F44" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F44" s="2">
+      <c r="G44" s="2">
         <v>7.2</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>0.54</v>
       </c>
-      <c r="H44" s="2">
+      <c r="I44" s="2">
         <v>1.5</v>
       </c>
-      <c r="I44" s="2">
+      <c r="J44" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J44" s="2">
+      <c r="K44" s="2">
         <v>5.6</v>
       </c>
-      <c r="K44" s="4">
+      <c r="L44" s="4">
         <v>180</v>
       </c>
-      <c r="L44" s="2">
+      <c r="M44" s="2">
         <v>101.2</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>0.32</v>
       </c>
-      <c r="N44" s="2">
+      <c r="O44" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O44" s="2">
+      <c r="P44" s="2">
         <v>6.8</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1.6</v>
       </c>
-      <c r="Q44" s="4">
+      <c r="R44" s="4">
         <v>3580</v>
       </c>
-      <c r="R44" s="4">
+      <c r="S44" s="4">
         <v>301</v>
       </c>
-      <c r="S44" s="4">
+      <c r="T44" s="4">
         <v>607</v>
       </c>
-      <c r="T44" s="2">
+      <c r="U44" s="2">
         <v>23.5</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2023</v>
       </c>
       <c r="B45">
         <v>114</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D45" t="s">
         <v>306</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>100</v>
       </c>
-      <c r="E45" s="2">
+      <c r="F45" s="2">
         <v>8.4</v>
       </c>
-      <c r="F45" s="2">
+      <c r="G45" s="2">
         <v>7.2</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>0.84</v>
       </c>
-      <c r="H45" s="2">
+      <c r="I45" s="2">
         <v>1.6</v>
       </c>
-      <c r="I45" s="2">
+      <c r="J45" s="2">
         <v>5.2</v>
       </c>
-      <c r="J45" s="2">
+      <c r="K45" s="2">
         <v>5.9</v>
       </c>
-      <c r="K45" s="4">
+      <c r="L45" s="4">
         <v>155</v>
       </c>
-      <c r="L45" s="2">
+      <c r="M45" s="2">
         <v>128.80000000000001</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>0.26</v>
       </c>
-      <c r="N45" s="2">
+      <c r="O45" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O45" s="2">
+      <c r="P45" s="2">
         <v>5.3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>0.86</v>
       </c>
-      <c r="Q45" s="4">
+      <c r="R45" s="4">
         <v>4894</v>
       </c>
-      <c r="R45" s="4">
+      <c r="S45" s="4">
         <v>301</v>
       </c>
-      <c r="S45" s="4">
+      <c r="T45" s="4">
         <v>1023</v>
       </c>
-      <c r="T45" s="2">
+      <c r="U45" s="2">
         <v>31.8</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2023</v>
       </c>
       <c r="B46">
         <v>114</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D46" t="s">
         <v>306</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>140</v>
       </c>
-      <c r="E46" s="2">
+      <c r="F46" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F46" s="2">
+      <c r="G46" s="2">
         <v>7.2</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>0.66</v>
       </c>
-      <c r="H46" s="2">
+      <c r="I46" s="2">
         <v>1.3</v>
       </c>
-      <c r="I46" s="2">
+      <c r="J46" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J46" s="2">
+      <c r="K46" s="2">
         <v>5.8</v>
       </c>
-      <c r="K46" s="4">
+      <c r="L46" s="4">
         <v>115</v>
       </c>
-      <c r="L46" s="2">
+      <c r="M46" s="2">
         <v>136.19999999999999</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>0.2</v>
       </c>
-      <c r="N46" s="2">
+      <c r="O46" s="2">
         <v>3.7</v>
       </c>
-      <c r="O46" s="2">
+      <c r="P46" s="2">
         <v>3.9</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>0.64</v>
       </c>
-      <c r="Q46" s="4">
+      <c r="R46" s="4">
         <v>4805</v>
       </c>
-      <c r="R46" s="4">
+      <c r="S46" s="4">
         <v>302</v>
       </c>
-      <c r="S46" s="4">
+      <c r="T46" s="4">
         <v>565</v>
       </c>
-      <c r="T46" s="2">
+      <c r="U46" s="2">
         <v>29.3</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2023</v>
       </c>
       <c r="B47">
         <v>114</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D47" t="s">
         <v>306</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>180</v>
       </c>
-      <c r="E47" s="2">
+      <c r="F47" s="2">
         <v>8.1</v>
       </c>
-      <c r="F47" s="2">
+      <c r="G47" s="2">
         <v>7.2</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>0.52</v>
       </c>
-      <c r="H47" s="2">
+      <c r="I47" s="2">
         <v>1.5</v>
       </c>
-      <c r="I47" s="2">
+      <c r="J47" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J47" s="2">
+      <c r="K47" s="2">
         <v>6</v>
       </c>
-      <c r="K47" s="4">
+      <c r="L47" s="4">
         <v>149</v>
       </c>
-      <c r="L47" s="2">
+      <c r="M47" s="2">
         <v>112.3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>0.59</v>
       </c>
-      <c r="N47" s="2">
+      <c r="O47" s="2">
         <v>3.8</v>
       </c>
-      <c r="O47" s="2">
+      <c r="P47" s="2">
         <v>6.6</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>0.97</v>
       </c>
-      <c r="Q47" s="4">
+      <c r="R47" s="4">
         <v>4870</v>
       </c>
-      <c r="R47" s="4">
+      <c r="S47" s="4">
         <v>320</v>
       </c>
-      <c r="S47" s="4">
+      <c r="T47" s="4">
         <v>453</v>
       </c>
-      <c r="T47" s="2">
+      <c r="U47" s="2">
         <v>29.4</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2023</v>
       </c>
       <c r="B48">
         <v>114</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D48" t="s">
         <v>307</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>20</v>
       </c>
-      <c r="E48" s="2">
+      <c r="F48" s="2">
         <v>8.4</v>
       </c>
-      <c r="F48" s="2">
+      <c r="G48" s="2">
         <v>7.2</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>0.76</v>
       </c>
-      <c r="H48" s="2">
+      <c r="I48" s="2">
         <v>1.7</v>
       </c>
-      <c r="I48" s="2">
+      <c r="J48" s="2">
         <v>2.5</v>
       </c>
-      <c r="J48" s="2">
+      <c r="K48" s="2">
         <v>6.9</v>
       </c>
-      <c r="K48" s="4">
+      <c r="L48" s="4">
         <v>277</v>
       </c>
-      <c r="L48" s="2">
+      <c r="M48" s="2">
         <v>61.2</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>0.96</v>
       </c>
-      <c r="N48" s="2">
+      <c r="O48" s="2">
         <v>6.9</v>
       </c>
-      <c r="O48" s="2">
+      <c r="P48" s="2">
         <v>19.3</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3.17</v>
       </c>
-      <c r="Q48" s="4">
+      <c r="R48" s="4">
         <v>2960</v>
       </c>
-      <c r="R48" s="4">
+      <c r="S48" s="4">
         <v>248</v>
       </c>
-      <c r="S48" s="4">
+      <c r="T48" s="4">
         <v>618</v>
       </c>
-      <c r="T48" s="2">
+      <c r="U48" s="2">
         <v>20.3</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2023</v>
       </c>
       <c r="B49">
         <v>114</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D49" t="s">
         <v>307</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>60</v>
       </c>
-      <c r="E49" s="2">
+      <c r="F49" s="2">
         <v>8.5</v>
       </c>
-      <c r="F49" s="2">
+      <c r="G49" s="2">
         <v>7.2</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2.04</v>
       </c>
-      <c r="H49" s="2">
+      <c r="I49" s="2">
         <v>1.3</v>
       </c>
-      <c r="I49" s="2">
+      <c r="J49" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="J49" s="2">
+      <c r="K49" s="2">
         <v>6</v>
       </c>
-      <c r="K49" s="4">
+      <c r="L49" s="4">
         <v>175</v>
       </c>
-      <c r="L49" s="2">
+      <c r="M49" s="2">
         <v>164.7</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>0.32</v>
       </c>
-      <c r="N49" s="2">
+      <c r="O49" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O49" s="2">
+      <c r="P49" s="2">
         <v>7.4</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1.39</v>
       </c>
-      <c r="Q49" s="4">
+      <c r="R49" s="4">
         <v>4565</v>
       </c>
-      <c r="R49" s="4">
+      <c r="S49" s="4">
         <v>296</v>
       </c>
-      <c r="S49" s="4">
+      <c r="T49" s="4">
         <v>1003</v>
       </c>
-      <c r="T49" s="2">
+      <c r="U49" s="2">
         <v>30.1</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2023</v>
       </c>
       <c r="B50">
         <v>114</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D50" t="s">
         <v>307</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>100</v>
       </c>
-      <c r="E50" s="2">
+      <c r="F50" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F50" s="2">
+      <c r="G50" s="2">
         <v>7.2</v>
       </c>
-      <c r="G50" s="3">
+      <c r="H50" s="3">
         <v>1.94</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>1.2</v>
       </c>
-      <c r="I50" s="2">
+      <c r="J50" s="2">
         <v>2.8</v>
       </c>
-      <c r="J50" s="2">
+      <c r="K50" s="2">
         <v>6.1</v>
       </c>
-      <c r="K50" s="4">
+      <c r="L50" s="4">
         <v>111</v>
       </c>
-      <c r="L50" s="2">
+      <c r="M50" s="2">
         <v>185.7</v>
       </c>
-      <c r="M50" s="3">
+      <c r="N50" s="3">
         <v>0.3</v>
       </c>
-      <c r="N50" s="2">
+      <c r="O50" s="2">
         <v>4</v>
       </c>
-      <c r="O50" s="2">
+      <c r="P50" s="2">
         <v>2.7</v>
       </c>
-      <c r="P50" s="3">
+      <c r="Q50" s="3">
         <v>0.65</v>
       </c>
-      <c r="Q50" s="4">
+      <c r="R50" s="4">
         <v>4712</v>
       </c>
-      <c r="R50" s="4">
+      <c r="S50" s="4">
         <v>275</v>
       </c>
-      <c r="S50" s="4">
+      <c r="T50" s="4">
         <v>731</v>
       </c>
-      <c r="T50" s="2">
+      <c r="U50" s="2">
         <v>29.3</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2023</v>
       </c>
       <c r="B51">
         <v>114</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D51" t="s">
         <v>307</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>140</v>
       </c>
-      <c r="E51" s="2">
+      <c r="F51" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F51" s="2">
+      <c r="G51" s="2">
         <v>7.2</v>
       </c>
-      <c r="G51" s="3">
+      <c r="H51" s="3">
         <v>1.3</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>1.2</v>
       </c>
-      <c r="I51" s="2">
+      <c r="J51" s="2">
         <v>1.9</v>
       </c>
-      <c r="J51" s="2">
+      <c r="K51" s="2">
         <v>5.7</v>
       </c>
-      <c r="K51" s="4">
+      <c r="L51" s="4">
         <v>92</v>
       </c>
-      <c r="L51" s="2">
+      <c r="M51" s="2">
         <v>98.9</v>
       </c>
-      <c r="M51" s="3">
+      <c r="N51" s="3">
         <v>0.18</v>
       </c>
-      <c r="N51" s="2">
+      <c r="O51" s="2">
         <v>3.4</v>
       </c>
-      <c r="O51" s="2">
+      <c r="P51" s="2">
         <v>1.6</v>
       </c>
-      <c r="P51" s="3">
+      <c r="Q51" s="3">
         <v>0.43</v>
       </c>
-      <c r="Q51" s="4">
+      <c r="R51" s="4">
         <v>4517</v>
       </c>
-      <c r="R51" s="4">
+      <c r="S51" s="4">
         <v>278</v>
       </c>
-      <c r="S51" s="4">
+      <c r="T51" s="4">
         <v>398</v>
       </c>
-      <c r="T51" s="2">
+      <c r="U51" s="2">
         <v>26.9</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2023</v>
       </c>
       <c r="B52">
         <v>114</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D52" t="s">
         <v>307</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>180</v>
       </c>
-      <c r="E52" s="2">
+      <c r="F52" s="2">
         <v>8.1</v>
       </c>
-      <c r="F52" s="2">
+      <c r="G52" s="2">
         <v>7.2</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1.05</v>
       </c>
-      <c r="H52" s="2">
+      <c r="I52" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I52" s="2">
+      <c r="J52" s="2">
         <v>1.7</v>
       </c>
-      <c r="J52" s="2">
+      <c r="K52" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="K52" s="4">
+      <c r="L52" s="4">
         <v>81</v>
       </c>
-      <c r="L52" s="2">
+      <c r="M52" s="2">
         <v>72.3</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>0.16</v>
       </c>
-      <c r="N52" s="2">
+      <c r="O52" s="2">
         <v>2.4</v>
       </c>
-      <c r="O52" s="2">
+      <c r="P52" s="2">
         <v>1.2</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q52" s="4">
+      <c r="R52" s="4">
         <v>4217</v>
       </c>
-      <c r="R52" s="4">
+      <c r="S52" s="4">
         <v>268</v>
       </c>
-      <c r="S52" s="4">
+      <c r="T52" s="4">
         <v>262</v>
       </c>
-      <c r="T52" s="2">
+      <c r="U52" s="2">
         <v>24.7</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2023</v>
       </c>
       <c r="B53">
         <v>114</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D53" t="s">
         <v>308</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>20</v>
       </c>
-      <c r="E53" s="2">
+      <c r="F53" s="2">
         <v>8.4</v>
       </c>
-      <c r="F53" s="2">
+      <c r="G53" s="2">
         <v>7.2</v>
       </c>
-      <c r="G53" s="3">
+      <c r="H53" s="3">
         <v>0.95</v>
       </c>
-      <c r="H53" s="2">
+      <c r="I53" s="2">
         <v>1.9</v>
       </c>
-      <c r="I53" s="2">
+      <c r="J53" s="2">
         <v>3.1</v>
       </c>
-      <c r="J53" s="2">
+      <c r="K53" s="2">
         <v>7.2</v>
       </c>
-      <c r="K53" s="4">
+      <c r="L53" s="4">
         <v>286</v>
       </c>
-      <c r="L53" s="2">
+      <c r="M53" s="2">
         <v>97.2</v>
       </c>
-      <c r="M53" s="3">
+      <c r="N53" s="3">
         <v>0.98</v>
       </c>
-      <c r="N53" s="2">
+      <c r="O53" s="2">
         <v>6.2</v>
       </c>
-      <c r="O53" s="2">
+      <c r="P53" s="2">
         <v>21.4</v>
       </c>
-      <c r="P53" s="3">
+      <c r="Q53" s="3">
         <v>3.14</v>
       </c>
-      <c r="Q53" s="4">
+      <c r="R53" s="4">
         <v>2471</v>
       </c>
-      <c r="R53" s="4">
+      <c r="S53" s="4">
         <v>234</v>
       </c>
-      <c r="S53" s="4">
+      <c r="T53" s="4">
         <v>524</v>
       </c>
-      <c r="T53" s="2">
+      <c r="U53" s="2">
         <v>17.3</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2023</v>
       </c>
       <c r="B54">
         <v>114</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D54" t="s">
         <v>308</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>60</v>
       </c>
-      <c r="E54" s="2">
+      <c r="F54" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F54" s="2">
+      <c r="G54" s="2">
         <v>7.2</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1.58</v>
       </c>
-      <c r="H54" s="2">
+      <c r="I54" s="2">
         <v>1.2</v>
       </c>
-      <c r="I54" s="2">
+      <c r="J54" s="2">
         <v>4.8</v>
       </c>
-      <c r="J54" s="2">
+      <c r="K54" s="2">
         <v>6.2</v>
       </c>
-      <c r="K54" s="4">
+      <c r="L54" s="4">
         <v>153</v>
       </c>
-      <c r="L54" s="2">
+      <c r="M54" s="2">
         <v>158.30000000000001</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N54" s="2">
+      <c r="O54" s="2">
         <v>4.8</v>
       </c>
-      <c r="O54" s="2">
+      <c r="P54" s="2">
         <v>6.8</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1.36</v>
       </c>
-      <c r="Q54" s="4">
+      <c r="R54" s="4">
         <v>3736</v>
       </c>
-      <c r="R54" s="4">
+      <c r="S54" s="4">
         <v>213</v>
       </c>
-      <c r="S54" s="4">
+      <c r="T54" s="4">
         <v>644</v>
       </c>
-      <c r="T54" s="2">
+      <c r="U54" s="2">
         <v>23.6</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2023</v>
       </c>
       <c r="B55">
         <v>114</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D55" t="s">
         <v>308</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>100</v>
       </c>
-      <c r="E55" s="2">
+      <c r="F55" s="2">
         <v>8.1</v>
       </c>
-      <c r="F55" s="2">
+      <c r="G55" s="2">
         <v>7.2</v>
       </c>
-      <c r="G55" s="3">
+      <c r="H55" s="3">
         <v>3.76</v>
       </c>
-      <c r="H55" s="2">
+      <c r="I55" s="2">
         <v>1.3</v>
       </c>
-      <c r="I55" s="2">
+      <c r="J55" s="2">
         <v>7.9</v>
       </c>
-      <c r="J55" s="2">
+      <c r="K55" s="2">
         <v>5.8</v>
       </c>
-      <c r="K55" s="4">
+      <c r="L55" s="4">
         <v>127</v>
       </c>
-      <c r="L55" s="2">
+      <c r="M55" s="2">
         <v>301.89999999999998</v>
       </c>
-      <c r="M55" s="3">
+      <c r="N55" s="3">
         <v>0.24</v>
       </c>
-      <c r="N55" s="2">
+      <c r="O55" s="2">
         <v>4.3</v>
       </c>
-      <c r="O55" s="2">
+      <c r="P55" s="2">
         <v>2.9</v>
       </c>
-      <c r="P55" s="3">
+      <c r="Q55" s="3">
         <v>0.67</v>
       </c>
-      <c r="Q55" s="4">
+      <c r="R55" s="4">
         <v>4897</v>
       </c>
-      <c r="R55" s="4">
+      <c r="S55" s="4">
         <v>263</v>
       </c>
-      <c r="S55" s="4">
+      <c r="T55" s="4">
         <v>736</v>
       </c>
-      <c r="T55" s="2">
+      <c r="U55" s="2">
         <v>30.2</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2023</v>
       </c>
       <c r="B56">
         <v>114</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D56" t="s">
         <v>308</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>140</v>
       </c>
-      <c r="E56" s="2">
+      <c r="F56" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F56" s="2">
+      <c r="G56" s="2">
         <v>7.2</v>
       </c>
-      <c r="G56" s="3">
+      <c r="H56" s="3">
         <v>1.58</v>
       </c>
-      <c r="H56" s="2">
+      <c r="I56" s="2">
         <v>1.3</v>
       </c>
-      <c r="I56" s="2">
+      <c r="J56" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J56" s="2">
+      <c r="K56" s="2">
         <v>5.7</v>
       </c>
-      <c r="K56" s="4">
+      <c r="L56" s="4">
         <v>87</v>
       </c>
-      <c r="L56" s="2">
+      <c r="M56" s="2">
         <v>103.9</v>
       </c>
-      <c r="M56" s="3">
+      <c r="N56" s="3">
         <v>0.27</v>
       </c>
-      <c r="N56" s="2">
+      <c r="O56" s="2">
         <v>2.9</v>
       </c>
-      <c r="O56" s="2">
+      <c r="P56" s="2">
         <v>1.9</v>
       </c>
-      <c r="P56" s="3">
+      <c r="Q56" s="3">
         <v>0.41</v>
       </c>
-      <c r="Q56" s="4">
+      <c r="R56" s="4">
         <v>4709</v>
       </c>
-      <c r="R56" s="4">
+      <c r="S56" s="4">
         <v>223</v>
       </c>
-      <c r="S56" s="4">
+      <c r="T56" s="4">
         <v>358</v>
       </c>
-      <c r="T56" s="2">
+      <c r="U56" s="2">
         <v>27.2</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2023</v>
       </c>
       <c r="B57">
         <v>114</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D57" t="s">
         <v>308</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>180</v>
       </c>
-      <c r="E57" s="2">
+      <c r="F57" s="2">
         <v>8.1</v>
       </c>
-      <c r="F57" s="2">
+      <c r="G57" s="2">
         <v>7.2</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1.1599999999999999</v>
       </c>
-      <c r="H57" s="2">
+      <c r="I57" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I57" s="2">
+      <c r="J57" s="2">
         <v>1.9</v>
       </c>
-      <c r="J57" s="2">
+      <c r="K57" s="2">
         <v>5.8</v>
       </c>
-      <c r="K57" s="4">
+      <c r="L57" s="4">
         <v>92</v>
       </c>
-      <c r="L57" s="2">
+      <c r="M57" s="2">
         <v>50.8</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N57" s="2">
+      <c r="O57" s="2">
         <v>3.2</v>
       </c>
-      <c r="O57" s="2">
+      <c r="P57" s="2">
         <v>2.1</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>0.38</v>
       </c>
-      <c r="Q57" s="4">
+      <c r="R57" s="4">
         <v>4429</v>
       </c>
-      <c r="R57" s="4">
+      <c r="S57" s="4">
         <v>232</v>
       </c>
-      <c r="S57" s="4">
+      <c r="T57" s="4">
         <v>246</v>
       </c>
-      <c r="T57" s="2">
+      <c r="U57" s="2">
         <v>25.4</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2023</v>
       </c>
       <c r="B58">
         <v>114</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D58" t="s">
         <v>309</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>20</v>
       </c>
-      <c r="E58" s="2">
+      <c r="F58" s="2">
         <v>8.4</v>
       </c>
-      <c r="F58" s="2">
+      <c r="G58" s="2">
         <v>7.2</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>0.3</v>
       </c>
-      <c r="H58" s="2">
+      <c r="I58" s="2">
         <v>1.8</v>
       </c>
-      <c r="I58" s="2">
+      <c r="J58" s="2">
         <v>1.6</v>
       </c>
-      <c r="J58" s="2">
+      <c r="K58" s="2">
         <v>6.4</v>
       </c>
-      <c r="K58" s="4">
+      <c r="L58" s="4">
         <v>241</v>
       </c>
-      <c r="L58" s="2">
+      <c r="M58" s="2">
         <v>25.4</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>0.84</v>
       </c>
-      <c r="N58" s="2">
+      <c r="O58" s="2">
         <v>7.4</v>
       </c>
-      <c r="O58" s="2">
+      <c r="P58" s="2">
         <v>17.8</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3.04</v>
       </c>
-      <c r="Q58" s="4">
+      <c r="R58" s="4">
         <v>2861</v>
       </c>
-      <c r="R58" s="4">
+      <c r="S58" s="4">
         <v>257</v>
       </c>
-      <c r="S58" s="4">
+      <c r="T58" s="4">
         <v>504</v>
       </c>
-      <c r="T58" s="2">
+      <c r="U58" s="2">
         <v>19.3</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2023</v>
       </c>
       <c r="B59">
         <v>114</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D59" t="s">
         <v>309</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>60</v>
       </c>
-      <c r="E59" s="2">
+      <c r="F59" s="2">
         <v>8.6</v>
       </c>
-      <c r="F59" s="2">
+      <c r="G59" s="2">
         <v>7.2</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>0.34</v>
       </c>
-      <c r="H59" s="2">
+      <c r="I59" s="2">
         <v>1.6</v>
       </c>
-      <c r="I59" s="2">
+      <c r="J59" s="2">
         <v>2.7</v>
       </c>
-      <c r="J59" s="2">
+      <c r="K59" s="2">
         <v>6.2</v>
       </c>
-      <c r="K59" s="4">
+      <c r="L59" s="4">
         <v>221</v>
       </c>
-      <c r="L59" s="2">
+      <c r="M59" s="2">
         <v>53.8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>0.45</v>
       </c>
-      <c r="N59" s="2">
+      <c r="O59" s="2">
         <v>6.5</v>
       </c>
-      <c r="O59" s="2">
+      <c r="P59" s="2">
         <v>7.6</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1.28</v>
       </c>
-      <c r="Q59" s="4">
+      <c r="R59" s="4">
         <v>3327</v>
       </c>
-      <c r="R59" s="4">
+      <c r="S59" s="4">
         <v>305</v>
       </c>
-      <c r="S59" s="4">
+      <c r="T59" s="4">
         <v>768</v>
       </c>
-      <c r="T59" s="2">
+      <c r="U59" s="2">
         <v>23.1</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2023</v>
       </c>
       <c r="B60">
         <v>114</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D60" t="s">
         <v>309</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>100</v>
       </c>
-      <c r="E60" s="2">
+      <c r="F60" s="2">
         <v>8.5</v>
       </c>
-      <c r="F60" s="2">
+      <c r="G60" s="2">
         <v>7.2</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>0.34</v>
       </c>
-      <c r="H60" s="2">
+      <c r="I60" s="2">
         <v>1.4</v>
       </c>
-      <c r="I60" s="2">
+      <c r="J60" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J60" s="2">
+      <c r="K60" s="2">
         <v>5.6</v>
       </c>
-      <c r="K60" s="4">
+      <c r="L60" s="4">
         <v>121</v>
       </c>
-      <c r="L60" s="2">
+      <c r="M60" s="2">
         <v>49.8</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>0.24</v>
       </c>
-      <c r="N60" s="2">
+      <c r="O60" s="2">
         <v>5.3</v>
       </c>
-      <c r="O60" s="2">
+      <c r="P60" s="2">
         <v>3.2</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>0.56000000000000005</v>
       </c>
-      <c r="Q60" s="4">
+      <c r="R60" s="4">
         <v>3973</v>
       </c>
-      <c r="R60" s="4">
+      <c r="S60" s="4">
         <v>270</v>
       </c>
-      <c r="S60" s="4">
+      <c r="T60" s="4">
         <v>572</v>
       </c>
-      <c r="T60" s="2">
+      <c r="U60" s="2">
         <v>24.9</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2023</v>
       </c>
       <c r="B61">
         <v>114</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D61" t="s">
         <v>309</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>140</v>
       </c>
-      <c r="E61" s="2">
+      <c r="F61" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F61" s="2">
+      <c r="G61" s="2">
         <v>7.2</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>0.3</v>
       </c>
-      <c r="H61" s="2">
+      <c r="I61" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I61" s="2">
+      <c r="J61" s="2">
         <v>4.3</v>
       </c>
-      <c r="J61" s="2">
+      <c r="K61" s="2">
         <v>5.6</v>
       </c>
-      <c r="K61" s="4">
+      <c r="L61" s="4">
         <v>82</v>
       </c>
-      <c r="L61" s="2">
+      <c r="M61" s="2">
         <v>43.6</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>0.17</v>
       </c>
-      <c r="N61" s="2">
+      <c r="O61" s="2">
         <v>3.5</v>
       </c>
-      <c r="O61" s="2">
+      <c r="P61" s="2">
         <v>1.6</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>0.28000000000000003</v>
       </c>
-      <c r="Q61" s="4">
+      <c r="R61" s="4">
         <v>4198</v>
       </c>
-      <c r="R61" s="4">
+      <c r="S61" s="4">
         <v>233</v>
       </c>
-      <c r="S61" s="4">
+      <c r="T61" s="4">
         <v>360</v>
       </c>
-      <c r="T61" s="2">
+      <c r="U61" s="2">
         <v>24.7</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2023</v>
       </c>
       <c r="B62">
         <v>114</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="5">
+        <v>45040</v>
+      </c>
+      <c r="D62" t="s">
         <v>309</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>180</v>
       </c>
-      <c r="E62" s="2">
+      <c r="F62" s="2">
         <v>8.6</v>
       </c>
-      <c r="F62" s="2">
+      <c r="G62" s="2">
         <v>7.2</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H62" s="2">
+      <c r="I62" s="2">
         <v>1.2</v>
       </c>
-      <c r="I62" s="2">
+      <c r="J62" s="2">
         <v>5</v>
       </c>
-      <c r="J62" s="2">
+      <c r="K62" s="2">
         <v>5.8</v>
       </c>
-      <c r="K62" s="4">
+      <c r="L62" s="4">
         <v>75</v>
       </c>
-      <c r="L62" s="2">
+      <c r="M62" s="2">
         <v>35.6</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>0.17</v>
       </c>
-      <c r="N62" s="2">
+      <c r="O62" s="2">
         <v>3.4</v>
       </c>
-      <c r="O62" s="2">
+      <c r="P62" s="2">
         <v>1.4</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q62" s="4">
+      <c r="R62" s="4">
         <v>4218</v>
       </c>
-      <c r="R62" s="4">
+      <c r="S62" s="4">
         <v>225</v>
       </c>
-      <c r="S62" s="4">
+      <c r="T62" s="4">
         <v>314</v>
       </c>
-      <c r="T62" s="2">
+      <c r="U62" s="2">
         <v>24.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
